--- a/hormuz_vulnerability_index_v4_russia_FINAL.xlsx
+++ b/hormuz_vulnerability_index_v4_russia_FINAL.xlsx
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B34" s="47" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C34" s="52" t="inlineStr">
@@ -4172,89 +4172,85 @@
         </is>
       </c>
       <c r="D34" s="52" t="n">
-        <v>0.506</v>
+        <v>0.508</v>
       </c>
       <c r="E34" s="46" t="n">
-        <v>0.5626</v>
+        <v>0.5346</v>
       </c>
       <c r="F34" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G34" s="46" t="n"/>
       <c r="H34" s="46" t="n">
-        <v>0.6286</v>
+        <v>0.6434</v>
       </c>
       <c r="I34" s="46" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="J34" s="46" t="n">
-        <v>0.3701</v>
+        <v>0.6381</v>
       </c>
       <c r="K34" s="46" t="n"/>
       <c r="L34" s="46" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="M34" s="46" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2371</v>
+      </c>
+      <c r="M34" s="46" t="n"/>
       <c r="N34" s="46" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="O34" s="46" t="n">
-        <v>0</v>
+        <v>0.1053</v>
       </c>
       <c r="P34" s="46" t="n"/>
       <c r="Q34" s="49" t="n">
-        <v>0.4641</v>
+        <v>0.7234</v>
       </c>
       <c r="R34" s="49" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="S34" s="50" t="n">
-        <v>0.215</v>
+        <v>0.801</v>
       </c>
       <c r="T34" s="49" t="n">
-        <v>0.9092</v>
+        <v>0.9906</v>
       </c>
       <c r="U34" s="49" t="n">
-        <v>0.8173</v>
+        <v>0.7145</v>
       </c>
       <c r="V34" s="49" t="n">
-        <v>0.1193</v>
+        <v>0.9789</v>
       </c>
       <c r="W34" s="49" t="n">
-        <v>0.775</v>
+        <v>0.2</v>
       </c>
       <c r="X34" s="49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y34" s="46" t="n"/>
       <c r="Z34" s="46" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AA34" s="46" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="AB34" s="51" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AC34" s="46" t="inlineStr">
-        <is>
-          <t>0.6627</t>
-        </is>
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="AB34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="46" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD34" s="46" t="n">
-        <v>0.188</v>
+        <v>0.68</v>
       </c>
       <c r="AE34" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="AF34" s="46" t="n">
-        <v>0.119</v>
+        <v>0.979</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -4263,7 +4259,7 @@
       </c>
       <c r="B35" s="47" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C35" s="52" t="inlineStr">
@@ -4272,58 +4268,58 @@
         </is>
       </c>
       <c r="D35" s="52" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="E35" s="46" t="n">
-        <v>0.5346</v>
+        <v>0.5661</v>
       </c>
       <c r="F35" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G35" s="46" t="n"/>
       <c r="H35" s="46" t="n">
-        <v>0.6434</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="I35" s="46" t="n">
-        <v>0.647</v>
+        <v>0.7815</v>
       </c>
       <c r="J35" s="46" t="n">
-        <v>0.6381</v>
+        <v>0.8274</v>
       </c>
       <c r="K35" s="46" t="n"/>
       <c r="L35" s="46" t="n">
-        <v>0.2371</v>
+        <v>0.1956</v>
       </c>
       <c r="M35" s="46" t="n"/>
       <c r="N35" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O35" s="46" t="n">
-        <v>0.1053</v>
+        <v>0.0154</v>
       </c>
       <c r="P35" s="46" t="n"/>
       <c r="Q35" s="49" t="n">
-        <v>0.7234</v>
+        <v>0.7029</v>
       </c>
       <c r="R35" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S35" s="50" t="n">
-        <v>0.801</v>
+        <v>0.757</v>
       </c>
       <c r="T35" s="49" t="n">
-        <v>0.9906</v>
+        <v>0.9998</v>
       </c>
       <c r="U35" s="49" t="n">
-        <v>0.7145</v>
+        <v>0.5203</v>
       </c>
       <c r="V35" s="49" t="n">
-        <v>0.9789</v>
+        <v>0.9973</v>
       </c>
       <c r="W35" s="49" t="n">
-        <v>0.2</v>
+        <v>0.475</v>
       </c>
       <c r="X35" s="49" t="inlineStr">
         <is>
@@ -4332,25 +4328,27 @@
       </c>
       <c r="Y35" s="46" t="n"/>
       <c r="Z35" s="46" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="46" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="AB35" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC35" s="46" t="n">
-        <v>0.5</v>
+      <c r="AC35" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD35" s="46" t="n">
-        <v>0.68</v>
+        <v>0.823</v>
       </c>
       <c r="AE35" s="46" t="n">
-        <v>0.2</v>
+        <v>0.85</v>
       </c>
       <c r="AF35" s="46" t="n">
-        <v>0.979</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -4359,7 +4357,7 @@
       </c>
       <c r="B36" s="47" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Dominican Rep.</t>
         </is>
       </c>
       <c r="C36" s="52" t="inlineStr">
@@ -4368,10 +4366,10 @@
         </is>
       </c>
       <c r="D36" s="52" t="n">
-        <v>0.509</v>
+        <v>0.512</v>
       </c>
       <c r="E36" s="46" t="n">
-        <v>0.5661</v>
+        <v>0.5693</v>
       </c>
       <c r="F36" s="46" t="inlineStr">
         <is>
@@ -4380,43 +4378,39 @@
       </c>
       <c r="G36" s="46" t="n"/>
       <c r="H36" s="46" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="I36" s="46" t="n">
-        <v>0.7815</v>
+        <v>0.834</v>
       </c>
       <c r="J36" s="46" t="n">
-        <v>0.8274</v>
+        <v>0.5976</v>
       </c>
       <c r="K36" s="46" t="n"/>
       <c r="L36" s="46" t="n">
-        <v>0.1956</v>
+        <v>0.35</v>
       </c>
       <c r="M36" s="46" t="n"/>
-      <c r="N36" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O36" s="46" t="n">
-        <v>0.0154</v>
-      </c>
+      <c r="N36" s="46" t="n"/>
+      <c r="O36" s="46" t="n"/>
       <c r="P36" s="46" t="n"/>
       <c r="Q36" s="49" t="n">
-        <v>0.7029</v>
+        <v>0.6185</v>
       </c>
       <c r="R36" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S36" s="50" t="n">
-        <v>0.757</v>
+        <v>0.37</v>
       </c>
       <c r="T36" s="49" t="n">
-        <v>0.9998</v>
+        <v>0.952</v>
       </c>
       <c r="U36" s="49" t="n">
-        <v>0.5203</v>
+        <v>0.74</v>
       </c>
       <c r="V36" s="49" t="n">
-        <v>0.9973</v>
+        <v>0.6937</v>
       </c>
       <c r="W36" s="49" t="n">
         <v>0.475</v>
@@ -4431,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="AA36" s="46" t="n">
-        <v>0.659</v>
+        <v>0.821</v>
       </c>
       <c r="AB36" s="46" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AC36" s="46" t="inlineStr">
         <is>
@@ -4442,13 +4436,13 @@
         </is>
       </c>
       <c r="AD36" s="46" t="n">
-        <v>0.823</v>
+        <v>0.345</v>
       </c>
       <c r="AE36" s="46" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="AF36" s="46" t="n">
-        <v>0.997</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -4457,7 +4451,7 @@
       </c>
       <c r="B37" s="47" t="inlineStr">
         <is>
-          <t>Dominican Rep.</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C37" s="52" t="inlineStr">
@@ -4466,10 +4460,10 @@
         </is>
       </c>
       <c r="D37" s="52" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="E37" s="46" t="n">
-        <v>0.5693</v>
+        <v>0.5723</v>
       </c>
       <c r="F37" s="46" t="inlineStr">
         <is>
@@ -4478,42 +4472,46 @@
       </c>
       <c r="G37" s="46" t="n"/>
       <c r="H37" s="46" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7553</v>
       </c>
       <c r="I37" s="46" t="n">
-        <v>0.834</v>
+        <v>0.7365</v>
       </c>
       <c r="J37" s="46" t="n">
-        <v>0.5976</v>
+        <v>0.7836</v>
       </c>
       <c r="K37" s="46" t="n"/>
       <c r="L37" s="46" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="M37" s="46" t="n"/>
+      <c r="N37" s="46" t="n">
         <v>0.35</v>
       </c>
-      <c r="M37" s="46" t="n"/>
-      <c r="N37" s="46" t="n"/>
-      <c r="O37" s="46" t="n"/>
+      <c r="O37" s="46" t="n">
+        <v>0.09660000000000001</v>
+      </c>
       <c r="P37" s="46" t="n"/>
       <c r="Q37" s="49" t="n">
-        <v>0.6185</v>
+        <v>0.7286</v>
       </c>
       <c r="R37" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S37" s="50" t="n">
-        <v>0.37</v>
+        <v>0.795</v>
       </c>
       <c r="T37" s="49" t="n">
-        <v>0.952</v>
+        <v>0.9446</v>
       </c>
       <c r="U37" s="49" t="n">
-        <v>0.74</v>
+        <v>0.8008</v>
       </c>
       <c r="V37" s="49" t="n">
-        <v>0.6937</v>
+        <v>0.9431</v>
       </c>
       <c r="W37" s="49" t="n">
-        <v>0.475</v>
+        <v>0.325</v>
       </c>
       <c r="X37" s="49" t="inlineStr">
         <is>
@@ -4525,33 +4523,31 @@
         <v>0</v>
       </c>
       <c r="AA37" s="46" t="n">
-        <v>0.821</v>
+        <v>0.763</v>
       </c>
       <c r="AB37" s="46" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AC37" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AC37" s="46" t="n">
+        <v>0.55</v>
       </c>
       <c r="AD37" s="46" t="n">
-        <v>0.345</v>
+        <v>0.722</v>
       </c>
       <c r="AE37" s="46" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AF37" s="46" t="n">
-        <v>0.677</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="47" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C38" s="52" t="inlineStr">
@@ -4560,58 +4556,60 @@
         </is>
       </c>
       <c r="D38" s="52" t="n">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="E38" s="46" t="n">
-        <v>0.5723</v>
+        <v>0.647</v>
       </c>
       <c r="F38" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.80 (&lt;30d)</t>
         </is>
       </c>
       <c r="G38" s="46" t="n"/>
       <c r="H38" s="46" t="n">
-        <v>0.7553</v>
+        <v>0.6589</v>
       </c>
       <c r="I38" s="46" t="n">
-        <v>0.7365</v>
+        <v>0.78</v>
       </c>
       <c r="J38" s="46" t="n">
-        <v>0.7836</v>
+        <v>0.4773</v>
       </c>
       <c r="K38" s="46" t="n"/>
       <c r="L38" s="46" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="M38" s="46" t="n"/>
+        <v>0.5667</v>
+      </c>
+      <c r="M38" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="N38" s="46" t="n">
-        <v>0.35</v>
+        <v>0.3615</v>
       </c>
       <c r="O38" s="46" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.3006</v>
       </c>
       <c r="P38" s="46" t="n"/>
       <c r="Q38" s="49" t="n">
-        <v>0.7286</v>
+        <v>0.7153</v>
       </c>
       <c r="R38" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S38" s="50" t="n">
-        <v>0.795</v>
+        <v>1</v>
       </c>
       <c r="T38" s="49" t="n">
-        <v>0.9446</v>
+        <v>0.993</v>
       </c>
       <c r="U38" s="49" t="n">
-        <v>0.8008</v>
+        <v>0.4578</v>
       </c>
       <c r="V38" s="49" t="n">
-        <v>0.9431</v>
+        <v>0.8423</v>
       </c>
       <c r="W38" s="49" t="n">
-        <v>0.325</v>
+        <v>0.275</v>
       </c>
       <c r="X38" s="49" t="inlineStr">
         <is>
@@ -4620,34 +4618,36 @@
       </c>
       <c r="Y38" s="46" t="n"/>
       <c r="Z38" s="46" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA38" s="46" t="n">
-        <v>0.763</v>
+        <v>0.653</v>
       </c>
       <c r="AB38" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" s="46" t="n">
-        <v>0.55</v>
+      <c r="AC38" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD38" s="46" t="n">
-        <v>0.722</v>
+        <v>0.594</v>
       </c>
       <c r="AE38" s="46" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AF38" s="46" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="46" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="47" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C39" s="52" t="inlineStr">
@@ -4659,57 +4659,57 @@
         <v>0.518</v>
       </c>
       <c r="E39" s="46" t="n">
-        <v>0.647</v>
+        <v>0.5755</v>
       </c>
       <c r="F39" s="46" t="inlineStr">
         <is>
-          <t>0.80 (&lt;30d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G39" s="46" t="n"/>
       <c r="H39" s="46" t="n">
-        <v>0.6589</v>
+        <v>0.6936</v>
       </c>
       <c r="I39" s="46" t="n">
-        <v>0.78</v>
+        <v>0.763</v>
       </c>
       <c r="J39" s="46" t="n">
-        <v>0.4773</v>
+        <v>0.5895</v>
       </c>
       <c r="K39" s="46" t="n"/>
       <c r="L39" s="46" t="n">
-        <v>0.5667</v>
+        <v>0.4033</v>
       </c>
       <c r="M39" s="46" t="n">
-        <v>1</v>
+        <v>0.6939</v>
       </c>
       <c r="N39" s="46" t="n">
-        <v>0.3615</v>
+        <v>0.35</v>
       </c>
       <c r="O39" s="46" t="n">
-        <v>0.3006</v>
+        <v>0.1262</v>
       </c>
       <c r="P39" s="46" t="n"/>
       <c r="Q39" s="49" t="n">
-        <v>0.7153</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="R39" s="49" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S39" s="50" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="T39" s="49" t="n">
-        <v>0.993</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="U39" s="49" t="n">
-        <v>0.4578</v>
+        <v>0.74</v>
       </c>
       <c r="V39" s="49" t="n">
-        <v>0.8423</v>
+        <v>0.6937</v>
       </c>
       <c r="W39" s="49" t="n">
-        <v>0.275</v>
+        <v>0.475</v>
       </c>
       <c r="X39" s="49" t="inlineStr">
         <is>
@@ -4718,36 +4718,34 @@
       </c>
       <c r="Y39" s="46" t="n"/>
       <c r="Z39" s="46" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA39" s="46" t="n">
-        <v>0.653</v>
+        <v>0.875</v>
       </c>
       <c r="AB39" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0.122</v>
+      </c>
+      <c r="AC39" s="46" t="n">
+        <v>0.55</v>
       </c>
       <c r="AD39" s="46" t="n">
-        <v>0.594</v>
+        <v>0.11</v>
       </c>
       <c r="AE39" s="46" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="AF39" s="46" t="n">
-        <v>0.842</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="46" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C40" s="52" t="inlineStr">
@@ -4756,10 +4754,10 @@
         </is>
       </c>
       <c r="D40" s="52" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="E40" s="46" t="n">
-        <v>0.5755</v>
+        <v>0.5766</v>
       </c>
       <c r="F40" s="46" t="inlineStr">
         <is>
@@ -4768,48 +4766,46 @@
       </c>
       <c r="G40" s="46" t="n"/>
       <c r="H40" s="46" t="n">
-        <v>0.6936</v>
+        <v>0.7675</v>
       </c>
       <c r="I40" s="46" t="n">
-        <v>0.763</v>
+        <v>0.746</v>
       </c>
       <c r="J40" s="46" t="n">
-        <v>0.5895</v>
+        <v>0.7997</v>
       </c>
       <c r="K40" s="46" t="n"/>
       <c r="L40" s="46" t="n">
-        <v>0.4033</v>
-      </c>
-      <c r="M40" s="46" t="n">
-        <v>0.6939</v>
-      </c>
+        <v>0.2197</v>
+      </c>
+      <c r="M40" s="46" t="n"/>
       <c r="N40" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O40" s="46" t="n">
-        <v>0.1262</v>
+        <v>0.0677</v>
       </c>
       <c r="P40" s="46" t="n"/>
       <c r="Q40" s="49" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7427</v>
       </c>
       <c r="R40" s="49" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="S40" s="50" t="n">
-        <v>0.65</v>
+        <v>0.928</v>
       </c>
       <c r="T40" s="49" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.8954</v>
       </c>
       <c r="U40" s="49" t="n">
-        <v>0.74</v>
+        <v>0.7892</v>
       </c>
       <c r="V40" s="49" t="n">
-        <v>0.6937</v>
+        <v>0.9712</v>
       </c>
       <c r="W40" s="49" t="n">
-        <v>0.475</v>
+        <v>0.25</v>
       </c>
       <c r="X40" s="49" t="inlineStr">
         <is>
@@ -4818,25 +4814,25 @@
       </c>
       <c r="Y40" s="46" t="n"/>
       <c r="Z40" s="46" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="46" t="n">
-        <v>0.875</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AB40" s="46" t="n">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="46" t="n">
         <v>0.55</v>
       </c>
       <c r="AD40" s="46" t="n">
-        <v>0.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE40" s="46" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="AF40" s="46" t="n">
-        <v>0.677</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -4845,7 +4841,7 @@
       </c>
       <c r="B41" s="47" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C41" s="52" t="inlineStr">
@@ -4854,10 +4850,10 @@
         </is>
       </c>
       <c r="D41" s="52" t="n">
-        <v>0.519</v>
+        <v>0.522</v>
       </c>
       <c r="E41" s="46" t="n">
-        <v>0.5766</v>
+        <v>0.5795</v>
       </c>
       <c r="F41" s="46" t="inlineStr">
         <is>
@@ -4866,46 +4862,48 @@
       </c>
       <c r="G41" s="46" t="n"/>
       <c r="H41" s="46" t="n">
-        <v>0.7675</v>
+        <v>0.6533</v>
       </c>
       <c r="I41" s="46" t="n">
-        <v>0.746</v>
+        <v>0.829</v>
       </c>
       <c r="J41" s="46" t="n">
-        <v>0.7997</v>
+        <v>0.3897</v>
       </c>
       <c r="K41" s="46" t="n"/>
       <c r="L41" s="46" t="n">
-        <v>0.2197</v>
-      </c>
-      <c r="M41" s="46" t="n"/>
+        <v>0.4864</v>
+      </c>
+      <c r="M41" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="N41" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O41" s="46" t="n">
-        <v>0.0677</v>
+        <v>0.0463</v>
       </c>
       <c r="P41" s="46" t="n"/>
       <c r="Q41" s="49" t="n">
-        <v>0.7427</v>
+        <v>0.5987</v>
       </c>
       <c r="R41" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S41" s="50" t="n">
-        <v>0.928</v>
+        <v>0.347</v>
       </c>
       <c r="T41" s="49" t="n">
-        <v>0.8954</v>
+        <v>0.8905</v>
       </c>
       <c r="U41" s="49" t="n">
-        <v>0.7892</v>
+        <v>0.9584</v>
       </c>
       <c r="V41" s="49" t="n">
-        <v>0.9712</v>
+        <v>0.3364</v>
       </c>
       <c r="W41" s="49" t="n">
-        <v>0.25</v>
+        <v>0.475</v>
       </c>
       <c r="X41" s="49" t="inlineStr">
         <is>
@@ -4917,22 +4915,24 @@
         <v>0</v>
       </c>
       <c r="AA41" s="46" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="AB41" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="46" t="n">
-        <v>0.55</v>
+      <c r="AC41" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD41" s="46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="AE41" s="46" t="n">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="AF41" s="46" t="n">
-        <v>0.971</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C42" s="52" t="inlineStr">
@@ -4950,57 +4950,55 @@
         </is>
       </c>
       <c r="D42" s="52" t="n">
-        <v>0.522</v>
+        <v>0.524</v>
       </c>
       <c r="E42" s="46" t="n">
-        <v>0.5795</v>
+        <v>0.5517</v>
       </c>
       <c r="F42" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G42" s="46" t="n"/>
       <c r="H42" s="46" t="n">
-        <v>0.6533</v>
+        <v>0.7171</v>
       </c>
       <c r="I42" s="46" t="n">
-        <v>0.829</v>
+        <v>0.8285</v>
       </c>
       <c r="J42" s="46" t="n">
-        <v>0.3897</v>
+        <v>0.5501</v>
       </c>
       <c r="K42" s="46" t="n"/>
       <c r="L42" s="46" t="n">
-        <v>0.4864</v>
-      </c>
-      <c r="M42" s="46" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2341</v>
+      </c>
+      <c r="M42" s="46" t="n"/>
       <c r="N42" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O42" s="46" t="n">
-        <v>0.0463</v>
+        <v>0.0988</v>
       </c>
       <c r="P42" s="46" t="n"/>
       <c r="Q42" s="49" t="n">
-        <v>0.5987</v>
+        <v>0.7038</v>
       </c>
       <c r="R42" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S42" s="50" t="n">
-        <v>0.347</v>
+        <v>0.847</v>
       </c>
       <c r="T42" s="49" t="n">
-        <v>0.8905</v>
+        <v>0.6946</v>
       </c>
       <c r="U42" s="49" t="n">
-        <v>0.9584</v>
+        <v>0.8176</v>
       </c>
       <c r="V42" s="49" t="n">
-        <v>0.3364</v>
+        <v>0.9912</v>
       </c>
       <c r="W42" s="49" t="n">
         <v>0.475</v>
@@ -5015,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="46" t="n">
-        <v>0.891</v>
+        <v>0.892</v>
       </c>
       <c r="AB42" s="46" t="n">
         <v>0</v>
@@ -5026,22 +5024,22 @@
         </is>
       </c>
       <c r="AD42" s="46" t="n">
-        <v>0.217</v>
+        <v>0.694</v>
       </c>
       <c r="AE42" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="AF42" s="46" t="n">
-        <v>0.336</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="46" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C43" s="52" t="inlineStr">
@@ -5050,55 +5048,55 @@
         </is>
       </c>
       <c r="D43" s="52" t="n">
-        <v>0.524</v>
+        <v>0.525</v>
       </c>
       <c r="E43" s="46" t="n">
-        <v>0.5517</v>
+        <v>0.5834</v>
       </c>
       <c r="F43" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G43" s="46" t="n"/>
       <c r="H43" s="46" t="n">
-        <v>0.7171</v>
+        <v>0.6115</v>
       </c>
       <c r="I43" s="46" t="n">
-        <v>0.8285</v>
+        <v>0.7195</v>
       </c>
       <c r="J43" s="46" t="n">
-        <v>0.5501</v>
+        <v>0.4495</v>
       </c>
       <c r="K43" s="46" t="n"/>
       <c r="L43" s="46" t="n">
-        <v>0.2341</v>
-      </c>
-      <c r="M43" s="46" t="n"/>
+        <v>0.4781</v>
+      </c>
+      <c r="M43" s="46" t="n">
+        <v>0.5556</v>
+      </c>
       <c r="N43" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O43" s="46" t="n">
-        <v>0.0988</v>
-      </c>
+        <v>0.4005</v>
+      </c>
+      <c r="O43" s="46" t="n"/>
       <c r="P43" s="46" t="n"/>
       <c r="Q43" s="49" t="n">
-        <v>0.7038</v>
+        <v>0.6606</v>
       </c>
       <c r="R43" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S43" s="50" t="n">
-        <v>0.847</v>
+        <v>0.868</v>
       </c>
       <c r="T43" s="49" t="n">
-        <v>0.6946</v>
+        <v>0.9989</v>
       </c>
       <c r="U43" s="49" t="n">
-        <v>0.8176</v>
+        <v>0.6845</v>
       </c>
       <c r="V43" s="49" t="n">
-        <v>0.9912</v>
+        <v>0.1084</v>
       </c>
       <c r="W43" s="49" t="n">
         <v>0.475</v>
@@ -5113,33 +5111,31 @@
         <v>0</v>
       </c>
       <c r="AA43" s="46" t="n">
-        <v>0.892</v>
+        <v>0.678</v>
       </c>
       <c r="AB43" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC43" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+      <c r="AC43" s="46" t="n">
+        <v>0.55</v>
       </c>
       <c r="AD43" s="46" t="n">
-        <v>0.694</v>
+        <v>0.581</v>
       </c>
       <c r="AE43" s="46" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="AF43" s="46" t="n">
-        <v>0.991</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="46" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Other Asia, nes</t>
         </is>
       </c>
       <c r="C44" s="52" t="inlineStr">
@@ -5151,7 +5147,7 @@
         <v>0.525</v>
       </c>
       <c r="E44" s="46" t="n">
-        <v>0.5834</v>
+        <v>0.5837</v>
       </c>
       <c r="F44" s="46" t="inlineStr">
         <is>
@@ -5160,43 +5156,39 @@
       </c>
       <c r="G44" s="46" t="n"/>
       <c r="H44" s="46" t="n">
-        <v>0.6115</v>
+        <v>0.7234</v>
       </c>
       <c r="I44" s="46" t="n">
-        <v>0.7195</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="J44" s="46" t="n">
-        <v>0.4495</v>
+        <v>0.6284</v>
       </c>
       <c r="K44" s="46" t="n"/>
       <c r="L44" s="46" t="n">
-        <v>0.4781</v>
-      </c>
-      <c r="M44" s="46" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="N44" s="46" t="n">
-        <v>0.4005</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="M44" s="46" t="n"/>
+      <c r="N44" s="46" t="n"/>
       <c r="O44" s="46" t="n"/>
       <c r="P44" s="46" t="n"/>
       <c r="Q44" s="49" t="n">
-        <v>0.6606</v>
+        <v>0.6778</v>
       </c>
       <c r="R44" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S44" s="50" t="n">
-        <v>0.868</v>
+        <v>0.6565</v>
       </c>
       <c r="T44" s="49" t="n">
-        <v>0.9989</v>
+        <v>0.9618</v>
       </c>
       <c r="U44" s="49" t="n">
-        <v>0.6845</v>
+        <v>0.74</v>
       </c>
       <c r="V44" s="49" t="n">
-        <v>0.1084</v>
+        <v>0.6937</v>
       </c>
       <c r="W44" s="49" t="n">
         <v>0.475</v>
@@ -5211,31 +5203,33 @@
         <v>0</v>
       </c>
       <c r="AA44" s="46" t="n">
-        <v>0.678</v>
+        <v>0.758</v>
       </c>
       <c r="AB44" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="46" t="n">
-        <v>0.55</v>
+        <v>0.122</v>
+      </c>
+      <c r="AC44" s="46" t="inlineStr">
+        <is>
+          <t>0.7719</t>
+        </is>
       </c>
       <c r="AD44" s="46" t="n">
-        <v>0.581</v>
+        <v>0.345</v>
       </c>
       <c r="AE44" s="46" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="AF44" s="46" t="n">
-        <v>0.108</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="46" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="47" t="inlineStr">
         <is>
-          <t>Other Asia, nes</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C45" s="52" t="inlineStr">
@@ -5244,51 +5238,57 @@
         </is>
       </c>
       <c r="D45" s="52" t="n">
-        <v>0.525</v>
+        <v>0.528</v>
       </c>
       <c r="E45" s="46" t="n">
-        <v>0.5837</v>
+        <v>0.5556</v>
       </c>
       <c r="F45" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G45" s="46" t="n"/>
       <c r="H45" s="46" t="n">
-        <v>0.7234</v>
+        <v>0.7272</v>
       </c>
       <c r="I45" s="46" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="J45" s="46" t="n">
-        <v>0.6284</v>
+        <v>0.624</v>
       </c>
       <c r="K45" s="46" t="n"/>
       <c r="L45" s="46" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="M45" s="46" t="n">
+        <v>0.5447</v>
+      </c>
+      <c r="N45" s="46" t="n">
         <v>0.35</v>
       </c>
-      <c r="M45" s="46" t="n"/>
-      <c r="N45" s="46" t="n"/>
-      <c r="O45" s="46" t="n"/>
+      <c r="O45" s="46" t="n">
+        <v>0.08890000000000001</v>
+      </c>
       <c r="P45" s="46" t="n"/>
       <c r="Q45" s="49" t="n">
-        <v>0.6778</v>
+        <v>0.5999</v>
       </c>
       <c r="R45" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S45" s="50" t="n">
-        <v>0.6565</v>
+        <v>0.527</v>
       </c>
       <c r="T45" s="49" t="n">
-        <v>0.9618</v>
+        <v>0.5073</v>
       </c>
       <c r="U45" s="49" t="n">
-        <v>0.74</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="V45" s="49" t="n">
-        <v>0.6937</v>
+        <v>0.9507</v>
       </c>
       <c r="W45" s="49" t="n">
         <v>0.475</v>
@@ -5300,27 +5300,27 @@
       </c>
       <c r="Y45" s="46" t="n"/>
       <c r="Z45" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="46" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="AB45" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AA45" s="46" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="AB45" s="46" t="n">
-        <v>0.122</v>
-      </c>
       <c r="AC45" s="46" t="inlineStr">
         <is>
-          <t>0.7719</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD45" s="46" t="n">
-        <v>0.345</v>
+        <v>0.643</v>
       </c>
       <c r="AE45" s="46" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="AF45" s="46" t="n">
-        <v>0.677</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="B46" s="47" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>State of Palestine</t>
         </is>
       </c>
       <c r="C46" s="52" t="inlineStr">
@@ -5338,57 +5338,51 @@
         </is>
       </c>
       <c r="D46" s="52" t="n">
-        <v>0.528</v>
+        <v>0.529</v>
       </c>
       <c r="E46" s="46" t="n">
-        <v>0.5556</v>
+        <v>0.5883</v>
       </c>
       <c r="F46" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G46" s="46" t="n"/>
       <c r="H46" s="46" t="n">
-        <v>0.7272</v>
+        <v>0.7296</v>
       </c>
       <c r="I46" s="46" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="J46" s="46" t="n">
-        <v>0.624</v>
+        <v>0.6284</v>
       </c>
       <c r="K46" s="46" t="n"/>
       <c r="L46" s="46" t="n">
-        <v>0.3398</v>
-      </c>
-      <c r="M46" s="46" t="n">
-        <v>0.5447</v>
-      </c>
-      <c r="N46" s="46" t="n">
         <v>0.35</v>
       </c>
-      <c r="O46" s="46" t="n">
-        <v>0.08890000000000001</v>
-      </c>
+      <c r="M46" s="46" t="n"/>
+      <c r="N46" s="46" t="n"/>
+      <c r="O46" s="46" t="n"/>
       <c r="P46" s="46" t="n"/>
       <c r="Q46" s="49" t="n">
-        <v>0.5999</v>
+        <v>0.6854</v>
       </c>
       <c r="R46" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S46" s="50" t="n">
-        <v>0.527</v>
+        <v>0.6565</v>
       </c>
       <c r="T46" s="49" t="n">
-        <v>0.5073</v>
+        <v>1</v>
       </c>
       <c r="U46" s="49" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="V46" s="49" t="n">
-        <v>0.9507</v>
+        <v>0.6937</v>
       </c>
       <c r="W46" s="49" t="n">
         <v>0.475</v>
@@ -5400,13 +5394,13 @@
       </c>
       <c r="Y46" s="46" t="n"/>
       <c r="Z46" s="46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="46" t="n">
-        <v>0.853</v>
+        <v>0.639</v>
       </c>
       <c r="AB46" s="46" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="AC46" s="46" t="inlineStr">
         <is>
@@ -5414,13 +5408,13 @@
         </is>
       </c>
       <c r="AD46" s="46" t="n">
-        <v>0.643</v>
+        <v>0.345</v>
       </c>
       <c r="AE46" s="46" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="AF46" s="46" t="n">
-        <v>0.951</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -5429,7 +5423,7 @@
       </c>
       <c r="B47" s="47" t="inlineStr">
         <is>
-          <t>State of Palestine</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C47" s="52" t="inlineStr">
@@ -5438,10 +5432,10 @@
         </is>
       </c>
       <c r="D47" s="52" t="n">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="E47" s="46" t="n">
-        <v>0.5883</v>
+        <v>0.5884</v>
       </c>
       <c r="F47" s="46" t="inlineStr">
         <is>
@@ -5450,42 +5444,48 @@
       </c>
       <c r="G47" s="46" t="n"/>
       <c r="H47" s="46" t="n">
-        <v>0.7296</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="I47" s="46" t="n">
-        <v>0.797</v>
+        <v>0.7395</v>
       </c>
       <c r="J47" s="46" t="n">
-        <v>0.6284</v>
+        <v>0.4192</v>
       </c>
       <c r="K47" s="46" t="n"/>
       <c r="L47" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M47" s="46" t="n"/>
-      <c r="N47" s="46" t="n"/>
-      <c r="O47" s="46" t="n"/>
+        <v>0.5565</v>
+      </c>
+      <c r="M47" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="46" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="O47" s="46" t="n">
+        <v>0.178</v>
+      </c>
       <c r="P47" s="46" t="n"/>
       <c r="Q47" s="49" t="n">
-        <v>0.6854</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="R47" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S47" s="50" t="n">
-        <v>0.6565</v>
+        <v>0.453</v>
       </c>
       <c r="T47" s="49" t="n">
-        <v>1</v>
+        <v>0.8037</v>
       </c>
       <c r="U47" s="49" t="n">
-        <v>0.74</v>
+        <v>0.7823</v>
       </c>
       <c r="V47" s="49" t="n">
-        <v>0.6937</v>
+        <v>0.6107</v>
       </c>
       <c r="W47" s="49" t="n">
-        <v>0.475</v>
+        <v>0.35</v>
       </c>
       <c r="X47" s="49" t="inlineStr">
         <is>
@@ -5497,33 +5497,31 @@
         <v>0</v>
       </c>
       <c r="AA47" s="46" t="n">
-        <v>0.639</v>
+        <v>0.779</v>
       </c>
       <c r="AB47" s="46" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="AC47" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="46" t="n">
+        <v>0.55</v>
       </c>
       <c r="AD47" s="46" t="n">
-        <v>0.345</v>
+        <v>0.444</v>
       </c>
       <c r="AE47" s="46" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="AF47" s="46" t="n">
-        <v>0.677</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="46" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C48" s="52" t="inlineStr">
@@ -5532,60 +5530,60 @@
         </is>
       </c>
       <c r="D48" s="52" t="n">
-        <v>0.53</v>
+        <v>0.532</v>
       </c>
       <c r="E48" s="46" t="n">
-        <v>0.5884</v>
+        <v>0.6654</v>
       </c>
       <c r="F48" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.80 (&lt;30d)</t>
         </is>
       </c>
       <c r="G48" s="46" t="n"/>
       <c r="H48" s="46" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="I48" s="46" t="n">
-        <v>0.7395</v>
+        <v>0.7839</v>
       </c>
       <c r="J48" s="46" t="n">
-        <v>0.4192</v>
+        <v>0.3626</v>
       </c>
       <c r="K48" s="46" t="n"/>
       <c r="L48" s="46" t="n">
-        <v>0.5565</v>
+        <v>0.6431</v>
       </c>
       <c r="M48" s="46" t="n">
         <v>1</v>
       </c>
       <c r="N48" s="46" t="n">
-        <v>0.4374</v>
+        <v>0.4012</v>
       </c>
       <c r="O48" s="46" t="n">
-        <v>0.178</v>
+        <v>0.5089</v>
       </c>
       <c r="P48" s="46" t="n"/>
       <c r="Q48" s="49" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.7376</v>
       </c>
       <c r="R48" s="49" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="S48" s="50" t="n">
-        <v>0.453</v>
+        <v>1</v>
       </c>
       <c r="T48" s="49" t="n">
-        <v>0.8037</v>
+        <v>0.6368</v>
       </c>
       <c r="U48" s="49" t="n">
-        <v>0.7823</v>
+        <v>0.6332</v>
       </c>
       <c r="V48" s="49" t="n">
-        <v>0.6107</v>
+        <v>0.2647</v>
       </c>
       <c r="W48" s="49" t="n">
-        <v>0.35</v>
+        <v>0.675</v>
       </c>
       <c r="X48" s="49" t="inlineStr">
         <is>
@@ -5594,34 +5592,36 @@
       </c>
       <c r="Y48" s="46" t="n"/>
       <c r="Z48" s="46" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA48" s="46" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="AB48" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="46" t="n">
-        <v>0.55</v>
+        <v>0.907</v>
+      </c>
+      <c r="AB48" s="51" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AC48" s="46" t="inlineStr">
+        <is>
+          <t>0.6916</t>
+        </is>
       </c>
       <c r="AD48" s="46" t="n">
-        <v>0.444</v>
+        <v>0.391</v>
       </c>
       <c r="AE48" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="AF48" s="46" t="n">
-        <v>0.611</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="47" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C49" s="52" t="inlineStr">
@@ -5633,57 +5633,55 @@
         <v>0.532</v>
       </c>
       <c r="E49" s="46" t="n">
-        <v>0.6654</v>
+        <v>0.5907</v>
       </c>
       <c r="F49" s="46" t="inlineStr">
         <is>
-          <t>0.80 (&lt;30d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G49" s="46" t="n"/>
       <c r="H49" s="46" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.7736</v>
       </c>
       <c r="I49" s="46" t="n">
-        <v>0.7839</v>
+        <v>0.78</v>
       </c>
       <c r="J49" s="46" t="n">
-        <v>0.3626</v>
+        <v>0.7641</v>
       </c>
       <c r="K49" s="46" t="n"/>
       <c r="L49" s="46" t="n">
-        <v>0.6431</v>
-      </c>
-      <c r="M49" s="46" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3179</v>
+      </c>
+      <c r="M49" s="46" t="n"/>
       <c r="N49" s="46" t="n">
-        <v>0.4012</v>
+        <v>0.35</v>
       </c>
       <c r="O49" s="46" t="n">
-        <v>0.5089</v>
+        <v>0.2804</v>
       </c>
       <c r="P49" s="46" t="n"/>
       <c r="Q49" s="49" t="n">
-        <v>0.7376</v>
+        <v>0.6807</v>
       </c>
       <c r="R49" s="49" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="S49" s="50" t="n">
-        <v>1</v>
+        <v>0.544</v>
       </c>
       <c r="T49" s="49" t="n">
-        <v>0.6368</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="U49" s="49" t="n">
-        <v>0.6332</v>
+        <v>0.7042</v>
       </c>
       <c r="V49" s="49" t="n">
-        <v>0.2647</v>
+        <v>0.971</v>
       </c>
       <c r="W49" s="49" t="n">
-        <v>0.675</v>
+        <v>0.475</v>
       </c>
       <c r="X49" s="49" t="inlineStr">
         <is>
@@ -5692,36 +5690,34 @@
       </c>
       <c r="Y49" s="46" t="n"/>
       <c r="Z49" s="46" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="46" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="AB49" s="51" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="AC49" s="46" t="inlineStr">
-        <is>
-          <t>0.6916</t>
-        </is>
+        <v>0.919</v>
+      </c>
+      <c r="AB49" s="46" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AC49" s="46" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD49" s="46" t="n">
-        <v>0.391</v>
+        <v>0.453</v>
       </c>
       <c r="AE49" s="46" t="n">
-        <v>0.2</v>
+        <v>0.85</v>
       </c>
       <c r="AF49" s="46" t="n">
-        <v>0.265</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" s="47" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C50" s="52" t="inlineStr">
@@ -5733,52 +5729,50 @@
         <v>0.532</v>
       </c>
       <c r="E50" s="46" t="n">
-        <v>0.5907</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F50" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G50" s="46" t="n"/>
       <c r="H50" s="46" t="n">
-        <v>0.7736</v>
+        <v>0.6726</v>
       </c>
       <c r="I50" s="46" t="n">
-        <v>0.78</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J50" s="46" t="n">
-        <v>0.7641</v>
+        <v>0.5799</v>
       </c>
       <c r="K50" s="46" t="n"/>
       <c r="L50" s="46" t="n">
-        <v>0.3179</v>
+        <v>0.35</v>
       </c>
       <c r="M50" s="46" t="n"/>
       <c r="N50" s="46" t="n">
         <v>0.35</v>
       </c>
-      <c r="O50" s="46" t="n">
-        <v>0.2804</v>
-      </c>
+      <c r="O50" s="46" t="n"/>
       <c r="P50" s="46" t="n"/>
       <c r="Q50" s="49" t="n">
-        <v>0.6807</v>
+        <v>0.6573</v>
       </c>
       <c r="R50" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S50" s="50" t="n">
-        <v>0.544</v>
+        <v>0.981</v>
       </c>
       <c r="T50" s="49" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.4359</v>
       </c>
       <c r="U50" s="49" t="n">
-        <v>0.7042</v>
+        <v>0.8609</v>
       </c>
       <c r="V50" s="49" t="n">
-        <v>0.971</v>
+        <v>0.7099</v>
       </c>
       <c r="W50" s="49" t="n">
         <v>0.475</v>
@@ -5790,25 +5784,27 @@
       </c>
       <c r="Y50" s="46" t="n"/>
       <c r="Z50" s="46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA50" s="46" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="AB50" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AA50" s="46" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="AB50" s="46" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AC50" s="46" t="n">
-        <v>0.5</v>
+      <c r="AC50" s="46" t="inlineStr">
+        <is>
+          <t>0.8095</t>
+        </is>
       </c>
       <c r="AD50" s="46" t="n">
-        <v>0.453</v>
+        <v>0.83</v>
       </c>
       <c r="AE50" s="46" t="n">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="AF50" s="46" t="n">
-        <v>0.971</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
@@ -5817,7 +5813,7 @@
       </c>
       <c r="B51" s="47" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C51" s="52" t="inlineStr">
@@ -5826,56 +5822,60 @@
         </is>
       </c>
       <c r="D51" s="52" t="n">
-        <v>0.532</v>
+        <v>0.535</v>
       </c>
       <c r="E51" s="46" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5944</v>
       </c>
       <c r="F51" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G51" s="46" t="n"/>
       <c r="H51" s="46" t="n">
-        <v>0.6726</v>
+        <v>0.6891</v>
       </c>
       <c r="I51" s="46" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.952</v>
       </c>
       <c r="J51" s="46" t="n">
-        <v>0.5799</v>
+        <v>0.2948</v>
       </c>
       <c r="K51" s="46" t="n"/>
       <c r="L51" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M51" s="46" t="n"/>
+        <v>0.3576</v>
+      </c>
+      <c r="M51" s="46" t="n">
+        <v>0.6457000000000001</v>
+      </c>
       <c r="N51" s="46" t="n">
         <v>0.35</v>
       </c>
-      <c r="O51" s="46" t="n"/>
+      <c r="O51" s="46" t="n">
+        <v>0.0304</v>
+      </c>
       <c r="P51" s="46" t="n"/>
       <c r="Q51" s="49" t="n">
-        <v>0.6573</v>
+        <v>0.7365</v>
       </c>
       <c r="R51" s="49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="S51" s="50" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="T51" s="49" t="n">
+        <v>0.9604</v>
+      </c>
+      <c r="U51" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="49" t="n">
         <v>0.5</v>
-      </c>
-      <c r="S51" s="50" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="T51" s="49" t="n">
-        <v>0.4359</v>
-      </c>
-      <c r="U51" s="49" t="n">
-        <v>0.8609</v>
-      </c>
-      <c r="V51" s="49" t="n">
-        <v>0.7099</v>
-      </c>
-      <c r="W51" s="49" t="n">
-        <v>0.475</v>
       </c>
       <c r="X51" s="49" t="inlineStr">
         <is>
@@ -5884,27 +5884,27 @@
       </c>
       <c r="Y51" s="46" t="n"/>
       <c r="Z51" s="46" t="n">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA51" s="46" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="AB51" s="46" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AB51" s="51" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="AC51" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="AD51" s="46" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AE51" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF51" s="46" t="n">
         <v>0</v>
-      </c>
-      <c r="AC51" s="46" t="inlineStr">
-        <is>
-          <t>0.8095</t>
-        </is>
-      </c>
-      <c r="AD51" s="46" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AE51" s="46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF51" s="46" t="n">
-        <v>0.71</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B52" s="47" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C52" s="52" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="D52" s="52" t="n">
-        <v>0.535</v>
+        <v>0.537</v>
       </c>
       <c r="E52" s="46" t="n">
-        <v>0.5944</v>
+        <v>0.5967</v>
       </c>
       <c r="F52" s="46" t="inlineStr">
         <is>
@@ -5934,48 +5934,46 @@
       </c>
       <c r="G52" s="46" t="n"/>
       <c r="H52" s="46" t="n">
-        <v>0.6891</v>
+        <v>0.6721</v>
       </c>
       <c r="I52" s="46" t="n">
-        <v>0.952</v>
+        <v>0.6685</v>
       </c>
       <c r="J52" s="46" t="n">
-        <v>0.2948</v>
+        <v>0.6775</v>
       </c>
       <c r="K52" s="46" t="n"/>
       <c r="L52" s="46" t="n">
-        <v>0.3576</v>
-      </c>
-      <c r="M52" s="46" t="n">
-        <v>0.6457000000000001</v>
-      </c>
+        <v>0.4616</v>
+      </c>
+      <c r="M52" s="46" t="n"/>
       <c r="N52" s="46" t="n">
-        <v>0.35</v>
+        <v>0.6586</v>
       </c>
       <c r="O52" s="46" t="n">
-        <v>0.0304</v>
+        <v>0.2318</v>
       </c>
       <c r="P52" s="46" t="n"/>
       <c r="Q52" s="49" t="n">
-        <v>0.7365</v>
+        <v>0.6563</v>
       </c>
       <c r="R52" s="49" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="S52" s="50" t="n">
-        <v>0.572</v>
+        <v>0.726</v>
       </c>
       <c r="T52" s="49" t="n">
-        <v>0.9604</v>
+        <v>0.6468</v>
       </c>
       <c r="U52" s="49" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V52" s="49" t="n">
-        <v>0</v>
+        <v>0.9156</v>
       </c>
       <c r="W52" s="49" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="X52" s="49" t="inlineStr">
         <is>
@@ -5984,27 +5982,25 @@
       </c>
       <c r="Y52" s="46" t="n"/>
       <c r="Z52" s="46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="46" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="AB52" s="51" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="AC52" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0.462</v>
+      </c>
+      <c r="AB52" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="46" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD52" s="46" t="n">
-        <v>0.573</v>
+        <v>0.653</v>
       </c>
       <c r="AE52" s="46" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AF52" s="46" t="n">
-        <v>0</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
@@ -6013,19 +6009,19 @@
       </c>
       <c r="B53" s="47" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
-        </is>
-      </c>
-      <c r="C53" s="52" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D53" s="52" t="n">
-        <v>0.537</v>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="C53" s="56" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="D53" s="56" t="n">
+        <v>0.543</v>
       </c>
       <c r="E53" s="46" t="n">
-        <v>0.5967</v>
+        <v>0.6031</v>
       </c>
       <c r="F53" s="46" t="inlineStr">
         <is>
@@ -6034,73 +6030,77 @@
       </c>
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="46" t="n">
-        <v>0.6721</v>
+        <v>0.6286</v>
       </c>
       <c r="I53" s="46" t="n">
-        <v>0.6685</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J53" s="46" t="n">
-        <v>0.6775</v>
+        <v>0.3701</v>
       </c>
       <c r="K53" s="46" t="n"/>
       <c r="L53" s="46" t="n">
-        <v>0.4616</v>
-      </c>
-      <c r="M53" s="46" t="n"/>
+        <v>0.7166</v>
+      </c>
+      <c r="M53" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="N53" s="46" t="n">
-        <v>0.6586</v>
+        <v>0.7</v>
       </c>
       <c r="O53" s="46" t="n">
-        <v>0.2318</v>
+        <v>0.6783</v>
       </c>
       <c r="P53" s="46" t="n"/>
       <c r="Q53" s="49" t="n">
-        <v>0.6563</v>
+        <v>0.4641</v>
       </c>
       <c r="R53" s="49" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="S53" s="50" t="n">
-        <v>0.726</v>
+        <v>0.215</v>
       </c>
       <c r="T53" s="49" t="n">
-        <v>0.6468</v>
+        <v>0.9092</v>
       </c>
       <c r="U53" s="49" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8173</v>
       </c>
       <c r="V53" s="49" t="n">
-        <v>0.9156</v>
+        <v>0.1193</v>
       </c>
       <c r="W53" s="49" t="n">
-        <v>0.35</v>
+        <v>0.775</v>
       </c>
       <c r="X53" s="49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="Y53" s="46" t="n"/>
       <c r="Z53" s="46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA53" s="46" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="AB53" s="51" t="n">
         <v>0.462</v>
       </c>
-      <c r="AB53" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="46" t="n">
-        <v>0.5</v>
+      <c r="AC53" s="46" t="inlineStr">
+        <is>
+          <t>0.6627</t>
+        </is>
       </c>
       <c r="AD53" s="46" t="n">
-        <v>0.653</v>
+        <v>0.188</v>
       </c>
       <c r="AE53" s="46" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="AF53" s="46" t="n">
-        <v>0.916</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Rep. of Korea</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C34" s="65" t="inlineStr">
@@ -14431,28 +14431,28 @@
         </is>
       </c>
       <c r="D34" s="65" t="n">
-        <v>0.506</v>
+        <v>0.508</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>0.5626</v>
+        <v>0.5346</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H34" s="19" t="n"/>
       <c r="I34" s="19" t="n">
-        <v>0.6286</v>
+        <v>0.6434</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.595</v>
+        <v>0.2371</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0.4641</v>
+        <v>0.7234</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C35" s="65" t="inlineStr">
@@ -14470,28 +14470,28 @@
         </is>
       </c>
       <c r="D35" s="65" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>0.5346</v>
+        <v>0.5661</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H35" s="19" t="n"/>
       <c r="I35" s="19" t="n">
-        <v>0.6434</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>0.2371</v>
+        <v>0.1956</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>0.7234</v>
+        <v>0.7029</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Dominican Rep.</t>
         </is>
       </c>
       <c r="C36" s="65" t="inlineStr">
@@ -14509,10 +14509,10 @@
         </is>
       </c>
       <c r="D36" s="65" t="n">
-        <v>0.509</v>
+        <v>0.512</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0.5661</v>
+        <v>0.5693</v>
       </c>
       <c r="F36" s="19" t="n">
         <v>0.9</v>
@@ -14524,13 +14524,13 @@
       </c>
       <c r="H36" s="19" t="n"/>
       <c r="I36" s="19" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0.1956</v>
+        <v>0.35</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0.7029</v>
+        <v>0.6185</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Dominican Rep.</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C37" s="65" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D37" s="65" t="n">
-        <v>0.512</v>
+        <v>0.515</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>0.5693</v>
+        <v>0.5723</v>
       </c>
       <c r="F37" s="19" t="n">
         <v>0.9</v>
@@ -14563,22 +14563,22 @@
       </c>
       <c r="H37" s="19" t="n"/>
       <c r="I37" s="19" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7553</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.35</v>
+        <v>0.233</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0.6185</v>
+        <v>0.7286</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C38" s="65" t="inlineStr">
@@ -14587,37 +14587,37 @@
         </is>
       </c>
       <c r="D38" s="65" t="n">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>0.5723</v>
+        <v>0.647</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&lt; 30 days (imminent)</t>
         </is>
       </c>
       <c r="H38" s="19" t="n"/>
       <c r="I38" s="19" t="n">
-        <v>0.7553</v>
+        <v>0.6589</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>0.233</v>
+        <v>0.5667</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>0.7286</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C39" s="65" t="inlineStr">
@@ -14629,34 +14629,34 @@
         <v>0.518</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>0.647</v>
+        <v>0.5755</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>&lt; 30 days (imminent)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H39" s="19" t="n"/>
       <c r="I39" s="19" t="n">
-        <v>0.6589</v>
+        <v>0.6936</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>0.5667</v>
+        <v>0.4033</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>0.7153</v>
+        <v>0.6294999999999999</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C40" s="65" t="inlineStr">
@@ -14665,10 +14665,10 @@
         </is>
       </c>
       <c r="D40" s="65" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="E40" s="19" t="n">
-        <v>0.5755</v>
+        <v>0.5766</v>
       </c>
       <c r="F40" s="19" t="n">
         <v>0.9</v>
@@ -14680,13 +14680,13 @@
       </c>
       <c r="H40" s="19" t="n"/>
       <c r="I40" s="19" t="n">
-        <v>0.6936</v>
+        <v>0.7675</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>0.4033</v>
+        <v>0.2197</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7427</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C41" s="65" t="inlineStr">
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="D41" s="65" t="n">
-        <v>0.519</v>
+        <v>0.522</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>0.5766</v>
+        <v>0.5795</v>
       </c>
       <c r="F41" s="19" t="n">
         <v>0.9</v>
@@ -14719,13 +14719,13 @@
       </c>
       <c r="H41" s="19" t="n"/>
       <c r="I41" s="19" t="n">
-        <v>0.7675</v>
+        <v>0.6533</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>0.2197</v>
+        <v>0.4864</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>0.7427</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C42" s="65" t="inlineStr">
@@ -14743,37 +14743,37 @@
         </is>
       </c>
       <c r="D42" s="65" t="n">
-        <v>0.522</v>
+        <v>0.524</v>
       </c>
       <c r="E42" s="19" t="n">
-        <v>0.5795</v>
+        <v>0.5517</v>
       </c>
       <c r="F42" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H42" s="19" t="n"/>
       <c r="I42" s="19" t="n">
-        <v>0.6533</v>
+        <v>0.7171</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>0.4864</v>
+        <v>0.2341</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>0.5987</v>
+        <v>0.7038</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C43" s="65" t="inlineStr">
@@ -14782,37 +14782,37 @@
         </is>
       </c>
       <c r="D43" s="65" t="n">
-        <v>0.524</v>
+        <v>0.525</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>0.5517</v>
+        <v>0.5834</v>
       </c>
       <c r="F43" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G43" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H43" s="19" t="n"/>
       <c r="I43" s="19" t="n">
-        <v>0.7171</v>
+        <v>0.6115</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>0.2341</v>
+        <v>0.4781</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>0.7038</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="19" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Other Asia, nes</t>
         </is>
       </c>
       <c r="C44" s="65" t="inlineStr">
@@ -14824,7 +14824,7 @@
         <v>0.525</v>
       </c>
       <c r="E44" s="19" t="n">
-        <v>0.5834</v>
+        <v>0.5837</v>
       </c>
       <c r="F44" s="19" t="n">
         <v>0.9</v>
@@ -14836,22 +14836,22 @@
       </c>
       <c r="H44" s="19" t="n"/>
       <c r="I44" s="19" t="n">
-        <v>0.6115</v>
+        <v>0.7234</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>0.4781</v>
+        <v>0.35</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>0.6606</v>
+        <v>0.6778</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Other Asia, nes</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C45" s="65" t="inlineStr">
@@ -14860,28 +14860,28 @@
         </is>
       </c>
       <c r="D45" s="65" t="n">
-        <v>0.525</v>
+        <v>0.528</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>0.5837</v>
+        <v>0.5556</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H45" s="19" t="n"/>
       <c r="I45" s="19" t="n">
-        <v>0.7234</v>
+        <v>0.7272</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>0.35</v>
+        <v>0.3398</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>0.6778</v>
+        <v>0.5999</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>State of Palestine</t>
         </is>
       </c>
       <c r="C46" s="65" t="inlineStr">
@@ -14899,28 +14899,28 @@
         </is>
       </c>
       <c r="D46" s="65" t="n">
-        <v>0.528</v>
+        <v>0.529</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>0.5556</v>
+        <v>0.5883</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H46" s="19" t="n"/>
       <c r="I46" s="19" t="n">
-        <v>0.7272</v>
+        <v>0.7296</v>
       </c>
       <c r="J46" s="19" t="n">
-        <v>0.3398</v>
+        <v>0.35</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>0.5999</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>State of Palestine</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C47" s="65" t="inlineStr">
@@ -14938,10 +14938,10 @@
         </is>
       </c>
       <c r="D47" s="65" t="n">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="E47" s="19" t="n">
-        <v>0.5883</v>
+        <v>0.5884</v>
       </c>
       <c r="F47" s="19" t="n">
         <v>0.9</v>
@@ -14953,22 +14953,22 @@
       </c>
       <c r="H47" s="19" t="n"/>
       <c r="I47" s="19" t="n">
-        <v>0.7296</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J47" s="19" t="n">
-        <v>0.35</v>
+        <v>0.5565</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>0.6854</v>
+        <v>0.5973000000000001</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C48" s="65" t="inlineStr">
@@ -14977,37 +14977,37 @@
         </is>
       </c>
       <c r="D48" s="65" t="n">
-        <v>0.53</v>
+        <v>0.532</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>0.5884</v>
+        <v>0.6654</v>
       </c>
       <c r="F48" s="19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&lt; 30 days (imminent)</t>
         </is>
       </c>
       <c r="H48" s="19" t="n"/>
       <c r="I48" s="19" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J48" s="19" t="n">
-        <v>0.5565</v>
+        <v>0.6431</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.7376</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C49" s="65" t="inlineStr">
@@ -15019,34 +15019,34 @@
         <v>0.532</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>0.6654</v>
+        <v>0.5907</v>
       </c>
       <c r="F49" s="19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G49" s="23" t="inlineStr">
         <is>
-          <t>&lt; 30 days (imminent)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H49" s="19" t="n"/>
       <c r="I49" s="19" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.7736</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>0.6431</v>
+        <v>0.3179</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>0.7376</v>
+        <v>0.6807</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C50" s="65" t="inlineStr">
@@ -15058,25 +15058,25 @@
         <v>0.532</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>0.5907</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H50" s="19" t="n"/>
       <c r="I50" s="19" t="n">
-        <v>0.7736</v>
+        <v>0.6726</v>
       </c>
       <c r="J50" s="19" t="n">
-        <v>0.3179</v>
+        <v>0.35</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>0.6807</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C51" s="65" t="inlineStr">
@@ -15094,28 +15094,28 @@
         </is>
       </c>
       <c r="D51" s="65" t="n">
-        <v>0.532</v>
+        <v>0.535</v>
       </c>
       <c r="E51" s="19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5944</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G51" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H51" s="19" t="n"/>
       <c r="I51" s="19" t="n">
-        <v>0.6726</v>
+        <v>0.6891</v>
       </c>
       <c r="J51" s="19" t="n">
-        <v>0.35</v>
+        <v>0.3576</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>0.6573</v>
+        <v>0.7365</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C52" s="65" t="inlineStr">
@@ -15133,10 +15133,10 @@
         </is>
       </c>
       <c r="D52" s="65" t="n">
-        <v>0.535</v>
+        <v>0.537</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>0.5944</v>
+        <v>0.5967</v>
       </c>
       <c r="F52" s="19" t="n">
         <v>0.9</v>
@@ -15148,13 +15148,13 @@
       </c>
       <c r="H52" s="19" t="n"/>
       <c r="I52" s="19" t="n">
-        <v>0.6891</v>
+        <v>0.6721</v>
       </c>
       <c r="J52" s="19" t="n">
-        <v>0.3576</v>
+        <v>0.4616</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>0.7365</v>
+        <v>0.6563</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
@@ -15163,19 +15163,19 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
-        </is>
-      </c>
-      <c r="C53" s="65" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="D53" s="65" t="n">
-        <v>0.537</v>
+          <t>Rep. of Korea</t>
+        </is>
+      </c>
+      <c r="C53" s="66" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="D53" s="66" t="n">
+        <v>0.543</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>0.5967</v>
+        <v>0.6031</v>
       </c>
       <c r="F53" s="19" t="n">
         <v>0.9</v>
@@ -15187,13 +15187,13 @@
       </c>
       <c r="H53" s="19" t="n"/>
       <c r="I53" s="19" t="n">
-        <v>0.6721</v>
+        <v>0.6286</v>
       </c>
       <c r="J53" s="19" t="n">
-        <v>0.4616</v>
+        <v>0.7166</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>0.6563</v>
+        <v>0.4641</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">

--- a/hormuz_vulnerability_index_v4_russia_FINAL.xlsx
+++ b/hormuz_vulnerability_index_v4_russia_FINAL.xlsx
@@ -8497,7 +8497,7 @@
       </c>
       <c r="B78" s="47" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C78" s="56" t="inlineStr">
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="D78" s="56" t="n">
-        <v>0.583</v>
+        <v>0.582</v>
       </c>
       <c r="E78" s="46" t="n">
-        <v>0.6478</v>
+        <v>0.6472</v>
       </c>
       <c r="F78" s="46" t="inlineStr">
         <is>
@@ -8518,52 +8518,52 @@
       </c>
       <c r="G78" s="46" t="n"/>
       <c r="H78" s="46" t="n">
-        <v>0.6651</v>
+        <v>0.6888</v>
       </c>
       <c r="I78" s="46" t="n">
-        <v>0.787</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J78" s="46" t="n">
-        <v>0.4822</v>
+        <v>0.4708</v>
       </c>
       <c r="K78" s="46" t="n"/>
       <c r="L78" s="46" t="n">
-        <v>0.4397</v>
+        <v>0.5275</v>
       </c>
       <c r="M78" s="46" t="n">
-        <v>0.8404</v>
+        <v>0.65</v>
       </c>
       <c r="N78" s="46" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O78" s="46" t="n">
-        <v>0.077</v>
+        <v>0.1832</v>
       </c>
       <c r="P78" s="46" t="n"/>
       <c r="Q78" s="49" t="n">
-        <v>0.8385</v>
+        <v>0.7254</v>
       </c>
       <c r="R78" s="49" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S78" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T78" s="49" t="n">
-        <v>0.9973</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="U78" s="49" t="n">
-        <v>0.7402</v>
+        <v>0.7439</v>
       </c>
       <c r="V78" s="49" t="n">
-        <v>0.8555</v>
+        <v>0.4598</v>
       </c>
       <c r="W78" s="49" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="X78" s="49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="Y78" s="46" t="n"/>
@@ -8571,22 +8571,24 @@
         <v>0</v>
       </c>
       <c r="AA78" s="46" t="n">
-        <v>0.872</v>
+        <v>0.909</v>
       </c>
       <c r="AB78" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" s="46" t="n">
-        <v>0.75</v>
+        <v>0.293</v>
+      </c>
+      <c r="AC78" s="46" t="inlineStr">
+        <is>
+          <t>0.7181</t>
+        </is>
       </c>
       <c r="AD78" s="46" t="n">
-        <v>0.305</v>
+        <v>0.428</v>
       </c>
       <c r="AE78" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF78" s="46" t="n">
-        <v>0.856</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -8595,7 +8597,7 @@
       </c>
       <c r="B79" s="47" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C79" s="56" t="inlineStr">
@@ -8604,10 +8606,10 @@
         </is>
       </c>
       <c r="D79" s="56" t="n">
-        <v>0.584</v>
+        <v>0.583</v>
       </c>
       <c r="E79" s="46" t="n">
-        <v>0.6491</v>
+        <v>0.6478</v>
       </c>
       <c r="F79" s="46" t="inlineStr">
         <is>
@@ -8616,48 +8618,48 @@
       </c>
       <c r="G79" s="46" t="n"/>
       <c r="H79" s="46" t="n">
-        <v>0.6909</v>
+        <v>0.6651</v>
       </c>
       <c r="I79" s="46" t="n">
-        <v>0.831</v>
+        <v>0.787</v>
       </c>
       <c r="J79" s="46" t="n">
-        <v>0.4807</v>
+        <v>0.4822</v>
       </c>
       <c r="K79" s="46" t="n"/>
       <c r="L79" s="46" t="n">
-        <v>0.4706</v>
+        <v>0.4397</v>
       </c>
       <c r="M79" s="46" t="n">
-        <v>0.6979</v>
+        <v>0.8404</v>
       </c>
       <c r="N79" s="46" t="n">
-        <v>0.4238</v>
+        <v>0.35</v>
       </c>
       <c r="O79" s="46" t="n">
-        <v>0.26</v>
+        <v>0.077</v>
       </c>
       <c r="P79" s="46" t="n"/>
       <c r="Q79" s="49" t="n">
-        <v>0.7857</v>
+        <v>0.8385</v>
       </c>
       <c r="R79" s="49" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="S79" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T79" s="49" t="n">
-        <v>0.6427</v>
+        <v>0.9973</v>
       </c>
       <c r="U79" s="49" t="n">
-        <v>0.5053</v>
+        <v>0.7402</v>
       </c>
       <c r="V79" s="49" t="n">
-        <v>0.9865</v>
+        <v>0.8555</v>
       </c>
       <c r="W79" s="49" t="n">
-        <v>0.375</v>
+        <v>0.35</v>
       </c>
       <c r="X79" s="49" t="inlineStr">
         <is>
@@ -8669,24 +8671,22 @@
         <v>0</v>
       </c>
       <c r="AA79" s="46" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AB79" s="51" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="AC79" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0.872</v>
+      </c>
+      <c r="AB79" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="46" t="n">
+        <v>0.75</v>
       </c>
       <c r="AD79" s="46" t="n">
-        <v>0.382</v>
+        <v>0.305</v>
       </c>
       <c r="AE79" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF79" s="46" t="n">
-        <v>0.987</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -8695,19 +8695,19 @@
       </c>
       <c r="B80" s="47" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
-        </is>
-      </c>
-      <c r="C80" s="58" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="D80" s="58" t="n">
-        <v>0.589</v>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C80" s="56" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="D80" s="56" t="n">
+        <v>0.584</v>
       </c>
       <c r="E80" s="46" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6491</v>
       </c>
       <c r="F80" s="46" t="inlineStr">
         <is>
@@ -8716,46 +8716,48 @@
       </c>
       <c r="G80" s="46" t="n"/>
       <c r="H80" s="46" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6909</v>
       </c>
       <c r="I80" s="46" t="n">
-        <v>0.8045</v>
+        <v>0.831</v>
       </c>
       <c r="J80" s="46" t="n">
-        <v>0.5511</v>
+        <v>0.4807</v>
       </c>
       <c r="K80" s="46" t="n"/>
       <c r="L80" s="46" t="n">
-        <v>0.5394</v>
+        <v>0.4706</v>
       </c>
       <c r="M80" s="46" t="n">
-        <v>0.7289</v>
+        <v>0.6979</v>
       </c>
       <c r="N80" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O80" s="46" t="n"/>
+        <v>0.4238</v>
+      </c>
+      <c r="O80" s="46" t="n">
+        <v>0.26</v>
+      </c>
       <c r="P80" s="46" t="n"/>
       <c r="Q80" s="49" t="n">
-        <v>0.7216</v>
+        <v>0.7857</v>
       </c>
       <c r="R80" s="49" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="S80" s="50" t="n">
-        <v>0.745</v>
+        <v>1</v>
       </c>
       <c r="T80" s="49" t="n">
-        <v>0.8296</v>
+        <v>0.6427</v>
       </c>
       <c r="U80" s="49" t="n">
-        <v>0.9929</v>
+        <v>0.5053</v>
       </c>
       <c r="V80" s="49" t="n">
-        <v>0.8274</v>
+        <v>0.9865</v>
       </c>
       <c r="W80" s="49" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="X80" s="49" t="inlineStr">
         <is>
@@ -8764,27 +8766,27 @@
       </c>
       <c r="Y80" s="46" t="n"/>
       <c r="Z80" s="46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA80" s="46" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="AB80" s="46" t="n">
-        <v>0</v>
+        <v>0.474</v>
+      </c>
+      <c r="AB80" s="51" t="n">
+        <v>0.577</v>
       </c>
       <c r="AC80" s="46" t="inlineStr">
         <is>
-          <t>0.9569</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD80" s="46" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="AE80" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF80" s="46" t="n">
-        <v>0.827</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
@@ -8793,7 +8795,7 @@
       </c>
       <c r="B81" s="47" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C81" s="58" t="inlineStr">
@@ -8802,10 +8804,10 @@
         </is>
       </c>
       <c r="D81" s="58" t="n">
-        <v>0.591</v>
+        <v>0.589</v>
       </c>
       <c r="E81" s="46" t="n">
-        <v>0.6571</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="F81" s="46" t="inlineStr">
         <is>
@@ -8814,46 +8816,46 @@
       </c>
       <c r="G81" s="46" t="n"/>
       <c r="H81" s="46" t="n">
-        <v>0.6712</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="I81" s="46" t="n">
-        <v>0.758</v>
+        <v>0.8045</v>
       </c>
       <c r="J81" s="46" t="n">
-        <v>0.5409</v>
+        <v>0.5511</v>
       </c>
       <c r="K81" s="46" t="n"/>
       <c r="L81" s="46" t="n">
-        <v>0.675</v>
+        <v>0.5394</v>
       </c>
       <c r="M81" s="46" t="n">
-        <v>0.65</v>
+        <v>0.7289</v>
       </c>
       <c r="N81" s="46" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="O81" s="46" t="n"/>
       <c r="P81" s="46" t="n"/>
       <c r="Q81" s="49" t="n">
-        <v>0.625</v>
+        <v>0.7216</v>
       </c>
       <c r="R81" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S81" s="50" t="n">
-        <v>0.381</v>
+        <v>0.745</v>
       </c>
       <c r="T81" s="49" t="n">
-        <v>0.893</v>
+        <v>0.8296</v>
       </c>
       <c r="U81" s="49" t="n">
-        <v>0.8268</v>
+        <v>0.9929</v>
       </c>
       <c r="V81" s="49" t="n">
-        <v>0.6743</v>
+        <v>0.8274</v>
       </c>
       <c r="W81" s="49" t="n">
-        <v>0.575</v>
+        <v>0.5</v>
       </c>
       <c r="X81" s="49" t="inlineStr">
         <is>
@@ -8862,25 +8864,27 @@
       </c>
       <c r="Y81" s="46" t="n"/>
       <c r="Z81" s="46" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AA81" s="46" t="n">
-        <v>0.885</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB81" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC81" s="46" t="n">
-        <v>0.55</v>
+      <c r="AC81" s="46" t="inlineStr">
+        <is>
+          <t>0.9569</t>
+        </is>
       </c>
       <c r="AD81" s="46" t="n">
-        <v>0.341</v>
+        <v>0.378</v>
       </c>
       <c r="AE81" s="46" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF81" s="46" t="n">
-        <v>0.674</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
@@ -8889,7 +8893,7 @@
       </c>
       <c r="B82" s="47" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C82" s="58" t="inlineStr">
@@ -8898,10 +8902,10 @@
         </is>
       </c>
       <c r="D82" s="58" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="E82" s="46" t="n">
-        <v>0.6582</v>
+        <v>0.6571</v>
       </c>
       <c r="F82" s="46" t="inlineStr">
         <is>
@@ -8910,48 +8914,46 @@
       </c>
       <c r="G82" s="46" t="n"/>
       <c r="H82" s="46" t="n">
-        <v>0.616</v>
+        <v>0.6712</v>
       </c>
       <c r="I82" s="46" t="n">
-        <v>0.867</v>
+        <v>0.758</v>
       </c>
       <c r="J82" s="46" t="n">
-        <v>0.2396</v>
+        <v>0.5409</v>
       </c>
       <c r="K82" s="46" t="n"/>
       <c r="L82" s="46" t="n">
-        <v>0.631</v>
+        <v>0.675</v>
       </c>
       <c r="M82" s="46" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="N82" s="46" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O82" s="46" t="n">
-        <v>0.5285</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="O82" s="46" t="n"/>
       <c r="P82" s="46" t="n"/>
       <c r="Q82" s="49" t="n">
-        <v>0.7275</v>
+        <v>0.625</v>
       </c>
       <c r="R82" s="49" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="S82" s="50" t="n">
-        <v>0.72</v>
+        <v>0.381</v>
       </c>
       <c r="T82" s="49" t="n">
-        <v>0.9084</v>
+        <v>0.893</v>
       </c>
       <c r="U82" s="49" t="n">
-        <v>0.731</v>
+        <v>0.8268</v>
       </c>
       <c r="V82" s="49" t="n">
-        <v>0.0472</v>
+        <v>0.6743</v>
       </c>
       <c r="W82" s="49" t="n">
-        <v>0.35</v>
+        <v>0.575</v>
       </c>
       <c r="X82" s="49" t="inlineStr">
         <is>
@@ -8960,27 +8962,25 @@
       </c>
       <c r="Y82" s="46" t="n"/>
       <c r="Z82" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA82" s="46" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AB82" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="46" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AD82" s="46" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AE82" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="AA82" s="46" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AB82" s="51" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="AC82" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="AD82" s="46" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AE82" s="46" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AF82" s="46" t="n">
-        <v>0.047</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="B83" s="47" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C83" s="58" t="inlineStr">
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="D83" s="58" t="n">
-        <v>0.601</v>
+        <v>0.592</v>
       </c>
       <c r="E83" s="46" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6582</v>
       </c>
       <c r="F83" s="46" t="inlineStr">
         <is>
@@ -9010,48 +9010,48 @@
       </c>
       <c r="G83" s="46" t="n"/>
       <c r="H83" s="46" t="n">
-        <v>0.7084</v>
+        <v>0.616</v>
       </c>
       <c r="I83" s="46" t="n">
-        <v>0.907</v>
+        <v>0.867</v>
       </c>
       <c r="J83" s="46" t="n">
-        <v>0.4105</v>
+        <v>0.2396</v>
       </c>
       <c r="K83" s="46" t="n"/>
       <c r="L83" s="46" t="n">
-        <v>0.4877</v>
+        <v>0.631</v>
       </c>
       <c r="M83" s="46" t="n">
-        <v>0.9547</v>
+        <v>1</v>
       </c>
       <c r="N83" s="46" t="n">
-        <v>0.4046</v>
+        <v>0.35</v>
       </c>
       <c r="O83" s="46" t="n">
-        <v>0.0398</v>
+        <v>0.5285</v>
       </c>
       <c r="P83" s="46" t="n"/>
       <c r="Q83" s="49" t="n">
-        <v>0.8073</v>
+        <v>0.7275</v>
       </c>
       <c r="R83" s="49" t="n">
         <v>0.9</v>
       </c>
       <c r="S83" s="50" t="n">
-        <v>0.843</v>
+        <v>0.72</v>
       </c>
       <c r="T83" s="49" t="n">
-        <v>0.8595</v>
+        <v>0.9084</v>
       </c>
       <c r="U83" s="49" t="n">
-        <v>0.7783</v>
+        <v>0.731</v>
       </c>
       <c r="V83" s="49" t="n">
-        <v>0.5629</v>
+        <v>0.0472</v>
       </c>
       <c r="W83" s="49" t="n">
-        <v>0.475</v>
+        <v>0.35</v>
       </c>
       <c r="X83" s="49" t="inlineStr">
         <is>
@@ -9060,25 +9060,27 @@
       </c>
       <c r="Y83" s="46" t="n"/>
       <c r="Z83" s="46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA83" s="46" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="AB83" s="46" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="AC83" s="46" t="n">
-        <v>0.9</v>
+        <v>0.406</v>
+      </c>
+      <c r="AB83" s="51" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="AC83" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD83" s="46" t="n">
-        <v>0.419</v>
+        <v>0.49</v>
       </c>
       <c r="AE83" s="46" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF83" s="46" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
@@ -9087,7 +9089,7 @@
       </c>
       <c r="B84" s="47" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C84" s="58" t="inlineStr">
@@ -9096,10 +9098,10 @@
         </is>
       </c>
       <c r="D84" s="58" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="E84" s="46" t="n">
-        <v>0.6716</v>
+        <v>0.6641</v>
       </c>
       <c r="F84" s="46" t="inlineStr">
         <is>
@@ -9108,73 +9110,77 @@
       </c>
       <c r="G84" s="46" t="n"/>
       <c r="H84" s="46" t="n">
-        <v>0.6639</v>
+        <v>0.6923</v>
       </c>
       <c r="I84" s="46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8035</v>
       </c>
       <c r="J84" s="46" t="n">
-        <v>0.6248</v>
+        <v>0.5254</v>
       </c>
       <c r="K84" s="46" t="n"/>
       <c r="L84" s="46" t="n">
-        <v>0.7183</v>
+        <v>0.6213</v>
       </c>
       <c r="M84" s="46" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="N84" s="46" t="n">
-        <v>0.4366</v>
-      </c>
-      <c r="O84" s="46" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="O84" s="46" t="n">
+        <v>0.4959</v>
+      </c>
       <c r="P84" s="46" t="n"/>
       <c r="Q84" s="49" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6787</v>
       </c>
       <c r="R84" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S84" s="50" t="n">
-        <v>0.516</v>
+        <v>0.613</v>
       </c>
       <c r="T84" s="49" t="n">
-        <v>0.8114</v>
+        <v>1</v>
       </c>
       <c r="U84" s="49" t="n">
-        <v>0.8295</v>
+        <v>0.6567</v>
       </c>
       <c r="V84" s="49" t="n">
-        <v>0.7391</v>
+        <v>0.7509</v>
       </c>
       <c r="W84" s="49" t="n">
-        <v>0.375</v>
+        <v>0.65</v>
       </c>
       <c r="X84" s="49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="Y84" s="46" t="n"/>
       <c r="Z84" s="46" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="46" t="n">
-        <v>0.578</v>
+        <v>0.765</v>
       </c>
       <c r="AB84" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AC84" s="46" t="n">
-        <v>0.5</v>
+      <c r="AC84" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD84" s="46" t="n">
-        <v>0.738</v>
+        <v>0.052</v>
       </c>
       <c r="AE84" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF84" s="46" t="n">
-        <v>0.739</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -9183,7 +9189,7 @@
       </c>
       <c r="B85" s="47" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C85" s="58" t="inlineStr">
@@ -9192,29 +9198,29 @@
         </is>
       </c>
       <c r="D85" s="58" t="n">
-        <v>0.608</v>
+        <v>0.598</v>
       </c>
       <c r="E85" s="46" t="n">
-        <v>0.6752</v>
+        <v>0.5976</v>
       </c>
       <c r="F85" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>1.00 (&gt;180d)</t>
         </is>
       </c>
       <c r="G85" s="46" t="n"/>
       <c r="H85" s="46" t="n">
-        <v>0.7052</v>
+        <v>0.7022</v>
       </c>
       <c r="I85" s="46" t="n">
-        <v>0.8075</v>
+        <v>0.8345</v>
       </c>
       <c r="J85" s="46" t="n">
-        <v>0.5517</v>
+        <v>0.5038</v>
       </c>
       <c r="K85" s="46" t="n"/>
       <c r="L85" s="46" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="M85" s="46" t="n">
         <v>0.65</v>
@@ -9222,28 +9228,30 @@
       <c r="N85" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O85" s="46" t="n"/>
+      <c r="O85" s="46" t="n">
+        <v>0.2718</v>
+      </c>
       <c r="P85" s="46" t="n"/>
       <c r="Q85" s="49" t="n">
-        <v>0.6455</v>
+        <v>0.5365</v>
       </c>
       <c r="R85" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S85" s="50" t="n">
-        <v>0.631</v>
+        <v>0.342</v>
       </c>
       <c r="T85" s="49" t="n">
-        <v>0.7857</v>
+        <v>0.9911</v>
       </c>
       <c r="U85" s="49" t="n">
-        <v>0.7783</v>
+        <v>0.4601</v>
       </c>
       <c r="V85" s="49" t="n">
-        <v>0.6288</v>
+        <v>0.1965</v>
       </c>
       <c r="W85" s="49" t="n">
-        <v>0.65</v>
+        <v>0.625</v>
       </c>
       <c r="X85" s="49" t="inlineStr">
         <is>
@@ -9255,7 +9263,7 @@
         <v>0</v>
       </c>
       <c r="AA85" s="46" t="n">
-        <v>0.784</v>
+        <v>0.919</v>
       </c>
       <c r="AB85" s="46" t="n">
         <v>0</v>
@@ -9266,13 +9274,13 @@
         </is>
       </c>
       <c r="AD85" s="46" t="n">
-        <v>0.445</v>
+        <v>0.359</v>
       </c>
       <c r="AE85" s="46" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="AF85" s="46" t="n">
-        <v>0.629</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
@@ -9281,7 +9289,7 @@
       </c>
       <c r="B86" s="47" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C86" s="58" t="inlineStr">
@@ -9290,10 +9298,10 @@
         </is>
       </c>
       <c r="D86" s="58" t="n">
-        <v>0.614</v>
+        <v>0.601</v>
       </c>
       <c r="E86" s="46" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="F86" s="46" t="inlineStr">
         <is>
@@ -9302,50 +9310,52 @@
       </c>
       <c r="G86" s="46" t="n"/>
       <c r="H86" s="46" t="n">
-        <v>0.6923</v>
+        <v>0.7084</v>
       </c>
       <c r="I86" s="46" t="n">
-        <v>0.8035</v>
+        <v>0.907</v>
       </c>
       <c r="J86" s="46" t="n">
-        <v>0.5254</v>
+        <v>0.4105</v>
       </c>
       <c r="K86" s="46" t="n"/>
       <c r="L86" s="46" t="n">
-        <v>0.675</v>
+        <v>0.4877</v>
       </c>
       <c r="M86" s="46" t="n">
-        <v>0.65</v>
+        <v>0.9547</v>
       </c>
       <c r="N86" s="46" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O86" s="46" t="n"/>
+        <v>0.4046</v>
+      </c>
+      <c r="O86" s="46" t="n">
+        <v>0.0398</v>
+      </c>
       <c r="P86" s="46" t="n"/>
       <c r="Q86" s="49" t="n">
-        <v>0.6787</v>
+        <v>0.8073</v>
       </c>
       <c r="R86" s="49" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="S86" s="50" t="n">
-        <v>0.613</v>
+        <v>0.843</v>
       </c>
       <c r="T86" s="49" t="n">
-        <v>1</v>
+        <v>0.8595</v>
       </c>
       <c r="U86" s="49" t="n">
-        <v>0.6567</v>
+        <v>0.7783</v>
       </c>
       <c r="V86" s="49" t="n">
-        <v>0.7509</v>
+        <v>0.5629</v>
       </c>
       <c r="W86" s="49" t="n">
-        <v>0.65</v>
+        <v>0.475</v>
       </c>
       <c r="X86" s="49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y86" s="46" t="n"/>
@@ -9353,24 +9363,22 @@
         <v>0</v>
       </c>
       <c r="AA86" s="46" t="n">
-        <v>0.765</v>
+        <v>0.866</v>
       </c>
       <c r="AB86" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC86" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0.659</v>
+      </c>
+      <c r="AC86" s="46" t="n">
+        <v>0.9</v>
       </c>
       <c r="AD86" s="46" t="n">
-        <v>0.052</v>
+        <v>0.419</v>
       </c>
       <c r="AE86" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF86" s="46" t="n">
-        <v>0.751</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
@@ -9379,7 +9387,7 @@
       </c>
       <c r="B87" s="47" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C87" s="58" t="inlineStr">
@@ -9388,89 +9396,85 @@
         </is>
       </c>
       <c r="D87" s="58" t="n">
-        <v>0.617</v>
+        <v>0.604</v>
       </c>
       <c r="E87" s="46" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6716</v>
       </c>
       <c r="F87" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G87" s="46" t="n"/>
       <c r="H87" s="46" t="n">
-        <v>0.6926</v>
+        <v>0.6639</v>
       </c>
       <c r="I87" s="46" t="n">
-        <v>0.756</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J87" s="46" t="n">
-        <v>0.5976</v>
+        <v>0.6248</v>
       </c>
       <c r="K87" s="46" t="n"/>
       <c r="L87" s="46" t="n">
-        <v>0.6073</v>
+        <v>0.7183</v>
       </c>
       <c r="M87" s="46" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N87" s="46" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O87" s="46" t="n">
-        <v>0.449</v>
-      </c>
+        <v>0.4366</v>
+      </c>
+      <c r="O87" s="46" t="n"/>
       <c r="P87" s="46" t="n"/>
       <c r="Q87" s="49" t="n">
-        <v>0.6492</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="R87" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S87" s="50" t="n">
-        <v>0.519</v>
+        <v>0.516</v>
       </c>
       <c r="T87" s="49" t="n">
-        <v>0.7435</v>
+        <v>0.8114</v>
       </c>
       <c r="U87" s="49" t="n">
-        <v>0.9497</v>
+        <v>0.8295</v>
       </c>
       <c r="V87" s="49" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.7391</v>
       </c>
       <c r="W87" s="49" t="n">
-        <v>0.7</v>
+        <v>0.375</v>
       </c>
       <c r="X87" s="49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y87" s="46" t="n"/>
       <c r="Z87" s="46" t="n">
-        <v>24.5</v>
+        <v>0.1</v>
       </c>
       <c r="AA87" s="46" t="n">
-        <v>0.835</v>
+        <v>0.578</v>
       </c>
       <c r="AB87" s="46" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AC87" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="AC87" s="46" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD87" s="46" t="n">
-        <v>0.161</v>
+        <v>0.738</v>
       </c>
       <c r="AE87" s="46" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AF87" s="46" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
@@ -9479,7 +9483,7 @@
       </c>
       <c r="B88" s="47" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C88" s="58" t="inlineStr">
@@ -9491,95 +9495,95 @@
         <v>0.617</v>
       </c>
       <c r="E88" s="46" t="n">
-        <v>0.6851</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F88" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G88" s="46" t="n"/>
       <c r="H88" s="46" t="n">
-        <v>0.666</v>
+        <v>0.6926</v>
       </c>
       <c r="I88" s="46" t="n">
-        <v>0.907</v>
+        <v>0.756</v>
       </c>
       <c r="J88" s="46" t="n">
-        <v>0.3044</v>
+        <v>0.5976</v>
       </c>
       <c r="K88" s="46" t="n"/>
       <c r="L88" s="46" t="n">
-        <v>0.6015</v>
+        <v>0.6073</v>
       </c>
       <c r="M88" s="46" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="N88" s="46" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O88" s="46" t="n">
-        <v>0.43</v>
+        <v>0.449</v>
       </c>
       <c r="P88" s="46" t="n"/>
       <c r="Q88" s="49" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.6492</v>
       </c>
       <c r="R88" s="49" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="S88" s="50" t="n">
-        <v>0.9</v>
+        <v>0.519</v>
       </c>
       <c r="T88" s="49" t="n">
-        <v>0.7527</v>
+        <v>0.7435</v>
       </c>
       <c r="U88" s="49" t="n">
-        <v>0.9983</v>
+        <v>0.9497</v>
       </c>
       <c r="V88" s="49" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W88" s="49" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="X88" s="49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="Y88" s="46" t="n"/>
       <c r="Z88" s="46" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="AA88" s="46" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AB88" s="51" t="n">
-        <v>0.858</v>
+        <v>0.835</v>
+      </c>
+      <c r="AB88" s="46" t="n">
+        <v>0.407</v>
       </c>
       <c r="AC88" s="46" t="inlineStr">
         <is>
-          <t>0.7440</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD88" s="46" t="n">
-        <v>0.345</v>
+        <v>0.161</v>
       </c>
       <c r="AE88" s="46" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="AF88" s="46" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="46" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C89" s="58" t="inlineStr">
@@ -9588,60 +9592,60 @@
         </is>
       </c>
       <c r="D89" s="58" t="n">
-        <v>0.621</v>
+        <v>0.617</v>
       </c>
       <c r="E89" s="46" t="n">
-        <v>0.6535</v>
+        <v>0.6851</v>
       </c>
       <c r="F89" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G89" s="46" t="n"/>
       <c r="H89" s="46" t="n">
-        <v>0.7175</v>
+        <v>0.666</v>
       </c>
       <c r="I89" s="46" t="n">
-        <v>0.861</v>
+        <v>0.907</v>
       </c>
       <c r="J89" s="46" t="n">
-        <v>0.5023</v>
+        <v>0.3044</v>
       </c>
       <c r="K89" s="46" t="n"/>
       <c r="L89" s="46" t="n">
-        <v>0.3839</v>
+        <v>0.6015</v>
       </c>
       <c r="M89" s="46" t="n">
-        <v>0.4096</v>
+        <v>1</v>
       </c>
       <c r="N89" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O89" s="46" t="n">
-        <v>0.3934</v>
+        <v>0.43</v>
       </c>
       <c r="P89" s="46" t="n"/>
       <c r="Q89" s="49" t="n">
-        <v>0.8591</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="R89" s="49" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="S89" s="50" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="T89" s="49" t="n">
-        <v>0.9586</v>
+        <v>0.7527</v>
       </c>
       <c r="U89" s="49" t="n">
-        <v>0.653</v>
+        <v>0.9983</v>
       </c>
       <c r="V89" s="49" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="W89" s="49" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="X89" s="49" t="inlineStr">
         <is>
@@ -9650,36 +9654,36 @@
       </c>
       <c r="Y89" s="46" t="n"/>
       <c r="Z89" s="46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AA89" s="46" t="n">
-        <v>0.871</v>
+        <v>0.833</v>
       </c>
       <c r="AB89" s="51" t="n">
-        <v>0.3</v>
+        <v>0.858</v>
       </c>
       <c r="AC89" s="46" t="inlineStr">
         <is>
-          <t>0.9561</t>
+          <t>0.7440</t>
         </is>
       </c>
       <c r="AD89" s="46" t="n">
-        <v>0.078</v>
+        <v>0.345</v>
       </c>
       <c r="AE89" s="46" t="n">
         <v>0.2</v>
       </c>
       <c r="AF89" s="46" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="46" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B90" s="47" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C90" s="58" t="inlineStr">
@@ -9691,57 +9695,57 @@
         <v>0.621</v>
       </c>
       <c r="E90" s="46" t="n">
-        <v>0.6902</v>
+        <v>0.6535</v>
       </c>
       <c r="F90" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G90" s="46" t="n"/>
       <c r="H90" s="46" t="n">
-        <v>0.7611</v>
+        <v>0.7175</v>
       </c>
       <c r="I90" s="46" t="n">
-        <v>0.9625</v>
+        <v>0.861</v>
       </c>
       <c r="J90" s="46" t="n">
-        <v>0.4591</v>
+        <v>0.5023</v>
       </c>
       <c r="K90" s="46" t="n"/>
       <c r="L90" s="46" t="n">
-        <v>0.6288</v>
+        <v>0.3839</v>
       </c>
       <c r="M90" s="46" t="n">
-        <v>1</v>
+        <v>0.4096</v>
       </c>
       <c r="N90" s="46" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="O90" s="46" t="n">
-        <v>0.1128</v>
+        <v>0.3934</v>
       </c>
       <c r="P90" s="46" t="n"/>
       <c r="Q90" s="49" t="n">
-        <v>0.6808</v>
+        <v>0.8591</v>
       </c>
       <c r="R90" s="49" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="S90" s="50" t="n">
-        <v>0.063</v>
+        <v>1</v>
       </c>
       <c r="T90" s="49" t="n">
-        <v>0.8576</v>
+        <v>0.9586</v>
       </c>
       <c r="U90" s="49" t="n">
-        <v>1</v>
+        <v>0.653</v>
       </c>
       <c r="V90" s="49" t="n">
-        <v>0.3697</v>
+        <v>0.8295</v>
       </c>
       <c r="W90" s="49" t="n">
-        <v>0.675</v>
+        <v>0.45</v>
       </c>
       <c r="X90" s="49" t="inlineStr">
         <is>
@@ -9750,34 +9754,36 @@
       </c>
       <c r="Y90" s="46" t="n"/>
       <c r="Z90" s="46" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA90" s="46" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="AB90" s="46" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AC90" s="46" t="n">
-        <v>0.92</v>
+        <v>0.871</v>
+      </c>
+      <c r="AB90" s="51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC90" s="46" t="inlineStr">
+        <is>
+          <t>0.9561</t>
+        </is>
       </c>
       <c r="AD90" s="46" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="AE90" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF90" s="46" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="46" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B91" s="47" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C91" s="58" t="inlineStr">
@@ -9786,10 +9792,10 @@
         </is>
       </c>
       <c r="D91" s="58" t="n">
-        <v>0.622</v>
+        <v>0.621</v>
       </c>
       <c r="E91" s="46" t="n">
-        <v>0.6913</v>
+        <v>0.6902</v>
       </c>
       <c r="F91" s="46" t="inlineStr">
         <is>
@@ -9798,48 +9804,48 @@
       </c>
       <c r="G91" s="46" t="n"/>
       <c r="H91" s="46" t="n">
-        <v>0.6192</v>
+        <v>0.7611</v>
       </c>
       <c r="I91" s="46" t="n">
-        <v>0.7595</v>
+        <v>0.9625</v>
       </c>
       <c r="J91" s="46" t="n">
-        <v>0.4088</v>
+        <v>0.4591</v>
       </c>
       <c r="K91" s="46" t="n"/>
       <c r="L91" s="46" t="n">
-        <v>0.7719</v>
+        <v>0.6288</v>
       </c>
       <c r="M91" s="46" t="n">
-        <v>0.9983</v>
+        <v>1</v>
       </c>
       <c r="N91" s="46" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O91" s="46" t="n">
-        <v>1</v>
+        <v>0.1128</v>
       </c>
       <c r="P91" s="46" t="n"/>
       <c r="Q91" s="49" t="n">
-        <v>0.6829</v>
+        <v>0.6808</v>
       </c>
       <c r="R91" s="49" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="S91" s="50" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="T91" s="49" t="n">
+        <v>0.8576</v>
+      </c>
+      <c r="U91" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="T91" s="49" t="n">
-        <v>0.9357</v>
-      </c>
-      <c r="U91" s="49" t="n">
-        <v>0.4942</v>
-      </c>
       <c r="V91" s="49" t="n">
-        <v>0.5286</v>
+        <v>0.3697</v>
       </c>
       <c r="W91" s="49" t="n">
-        <v>0.375</v>
+        <v>0.675</v>
       </c>
       <c r="X91" s="49" t="inlineStr">
         <is>
@@ -9851,22 +9857,22 @@
         <v>0</v>
       </c>
       <c r="AA91" s="46" t="n">
-        <v>0.88</v>
+        <v>0.891</v>
       </c>
       <c r="AB91" s="46" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AC91" s="46" t="n">
-        <v>0.55</v>
+        <v>0.92</v>
       </c>
       <c r="AD91" s="46" t="n">
-        <v>0.306</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AE91" s="46" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF91" s="46" t="n">
-        <v>0.529</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
@@ -9875,7 +9881,7 @@
       </c>
       <c r="B92" s="47" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C92" s="58" t="inlineStr">
@@ -9884,10 +9890,10 @@
         </is>
       </c>
       <c r="D92" s="58" t="n">
-        <v>0.625</v>
+        <v>0.622</v>
       </c>
       <c r="E92" s="46" t="n">
-        <v>0.6939</v>
+        <v>0.6913</v>
       </c>
       <c r="F92" s="46" t="inlineStr">
         <is>
@@ -9896,48 +9902,48 @@
       </c>
       <c r="G92" s="46" t="n"/>
       <c r="H92" s="46" t="n">
-        <v>0.774</v>
+        <v>0.6192</v>
       </c>
       <c r="I92" s="46" t="n">
-        <v>0.908</v>
+        <v>0.7595</v>
       </c>
       <c r="J92" s="46" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.4088</v>
       </c>
       <c r="K92" s="46" t="n"/>
       <c r="L92" s="46" t="n">
-        <v>0.4124</v>
+        <v>0.7719</v>
       </c>
       <c r="M92" s="46" t="n">
-        <v>0.8172</v>
+        <v>0.9983</v>
       </c>
       <c r="N92" s="46" t="n">
         <v>0.35</v>
       </c>
       <c r="O92" s="46" t="n">
-        <v>0.0129</v>
+        <v>1</v>
       </c>
       <c r="P92" s="46" t="n"/>
       <c r="Q92" s="49" t="n">
-        <v>0.8952</v>
+        <v>0.6829</v>
       </c>
       <c r="R92" s="49" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="S92" s="50" t="n">
-        <v>0.837</v>
+        <v>1</v>
       </c>
       <c r="T92" s="49" t="n">
-        <v>0.9745</v>
+        <v>0.9357</v>
       </c>
       <c r="U92" s="49" t="n">
-        <v>0.9774</v>
+        <v>0.4942</v>
       </c>
       <c r="V92" s="49" t="n">
-        <v>0.9877</v>
+        <v>0.5286</v>
       </c>
       <c r="W92" s="49" t="n">
-        <v>0.35</v>
+        <v>0.375</v>
       </c>
       <c r="X92" s="49" t="inlineStr">
         <is>
@@ -9946,25 +9952,25 @@
       </c>
       <c r="Y92" s="46" t="n"/>
       <c r="Z92" s="46" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="46" t="n">
-        <v>0.724</v>
+        <v>0.88</v>
       </c>
       <c r="AB92" s="46" t="n">
-        <v>0.859</v>
+        <v>0</v>
       </c>
       <c r="AC92" s="46" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="AD92" s="46" t="n">
-        <v>0.378</v>
+        <v>0.306</v>
       </c>
       <c r="AE92" s="46" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="AF92" s="46" t="n">
-        <v>0.988</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
@@ -9973,7 +9979,7 @@
       </c>
       <c r="B93" s="47" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C93" s="58" t="inlineStr">
@@ -9982,10 +9988,10 @@
         </is>
       </c>
       <c r="D93" s="58" t="n">
-        <v>0.627</v>
+        <v>0.625</v>
       </c>
       <c r="E93" s="46" t="n">
-        <v>0.6964</v>
+        <v>0.6939</v>
       </c>
       <c r="F93" s="46" t="inlineStr">
         <is>
@@ -9994,75 +10000,75 @@
       </c>
       <c r="G93" s="46" t="n"/>
       <c r="H93" s="46" t="n">
-        <v>0.6888</v>
+        <v>0.774</v>
       </c>
       <c r="I93" s="46" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.908</v>
       </c>
       <c r="J93" s="46" t="n">
-        <v>0.4708</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="K93" s="46" t="n"/>
       <c r="L93" s="46" t="n">
-        <v>0.675</v>
+        <v>0.4124</v>
       </c>
       <c r="M93" s="46" t="n">
-        <v>0.65</v>
+        <v>0.8172</v>
       </c>
       <c r="N93" s="46" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O93" s="46" t="n"/>
+        <v>0.35</v>
+      </c>
+      <c r="O93" s="46" t="n">
+        <v>0.0129</v>
+      </c>
       <c r="P93" s="46" t="n"/>
       <c r="Q93" s="49" t="n">
-        <v>0.7254</v>
+        <v>0.8952</v>
       </c>
       <c r="R93" s="49" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="S93" s="50" t="n">
-        <v>1</v>
+        <v>0.837</v>
       </c>
       <c r="T93" s="49" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9745</v>
       </c>
       <c r="U93" s="49" t="n">
-        <v>0.7439</v>
+        <v>0.9774</v>
       </c>
       <c r="V93" s="49" t="n">
-        <v>0.4598</v>
+        <v>0.9877</v>
       </c>
       <c r="W93" s="49" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="X93" s="49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y93" s="46" t="n"/>
       <c r="Z93" s="46" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA93" s="46" t="n">
-        <v>0.909</v>
+        <v>0.724</v>
       </c>
       <c r="AB93" s="46" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="AC93" s="46" t="inlineStr">
-        <is>
-          <t>0.7181</t>
-        </is>
+        <v>0.859</v>
+      </c>
+      <c r="AC93" s="46" t="n">
+        <v>0.9</v>
       </c>
       <c r="AD93" s="46" t="n">
-        <v>0.428</v>
+        <v>0.378</v>
       </c>
       <c r="AE93" s="46" t="n">
-        <v>0.2</v>
+        <v>0.88</v>
       </c>
       <c r="AF93" s="46" t="n">
-        <v>0.46</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
@@ -10263,7 +10269,7 @@
       </c>
       <c r="B96" s="47" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C96" s="58" t="inlineStr">
@@ -10272,10 +10278,10 @@
         </is>
       </c>
       <c r="D96" s="58" t="n">
-        <v>0.635</v>
+        <v>0.637</v>
       </c>
       <c r="E96" s="46" t="n">
-        <v>0.7052</v>
+        <v>0.7077</v>
       </c>
       <c r="F96" s="46" t="inlineStr">
         <is>
@@ -10284,17 +10290,17 @@
       </c>
       <c r="G96" s="46" t="n"/>
       <c r="H96" s="46" t="n">
-        <v>0.7153</v>
+        <v>0.7052</v>
       </c>
       <c r="I96" s="46" t="n">
-        <v>0.8175</v>
+        <v>0.8075</v>
       </c>
       <c r="J96" s="46" t="n">
-        <v>0.5619</v>
+        <v>0.5517</v>
       </c>
       <c r="K96" s="46" t="n"/>
       <c r="L96" s="46" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="M96" s="46" t="n">
         <v>0.65</v>
@@ -10302,28 +10308,30 @@
       <c r="N96" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O96" s="46" t="n"/>
+      <c r="O96" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P96" s="46" t="n"/>
       <c r="Q96" s="49" t="n">
-        <v>0.7252</v>
+        <v>0.6455</v>
       </c>
       <c r="R96" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S96" s="50" t="n">
-        <v>1</v>
+        <v>0.631</v>
       </c>
       <c r="T96" s="49" t="n">
-        <v>0.9782</v>
+        <v>0.7857</v>
       </c>
       <c r="U96" s="49" t="n">
-        <v>0.5567</v>
+        <v>0.7783</v>
       </c>
       <c r="V96" s="49" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6288</v>
       </c>
       <c r="W96" s="49" t="n">
-        <v>0.575</v>
+        <v>0.65</v>
       </c>
       <c r="X96" s="49" t="inlineStr">
         <is>
@@ -10335,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="AA96" s="46" t="n">
-        <v>0.833</v>
+        <v>0.784</v>
       </c>
       <c r="AB96" s="46" t="n">
         <v>0</v>
@@ -10346,13 +10354,13 @@
         </is>
       </c>
       <c r="AD96" s="46" t="n">
-        <v>0.316</v>
+        <v>0.445</v>
       </c>
       <c r="AE96" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF96" s="46" t="n">
-        <v>0.673</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
@@ -10361,7 +10369,7 @@
       </c>
       <c r="B97" s="47" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C97" s="58" t="inlineStr">
@@ -10370,29 +10378,29 @@
         </is>
       </c>
       <c r="D97" s="58" t="n">
-        <v>0.638</v>
+        <v>0.64</v>
       </c>
       <c r="E97" s="46" t="n">
-        <v>0.6379</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="F97" s="46" t="inlineStr">
         <is>
-          <t>1.00 (&gt;180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G97" s="46" t="n"/>
       <c r="H97" s="46" t="n">
-        <v>0.7022</v>
+        <v>0.7534</v>
       </c>
       <c r="I97" s="46" t="n">
-        <v>0.8345</v>
+        <v>0.876</v>
       </c>
       <c r="J97" s="46" t="n">
-        <v>0.5038</v>
+        <v>0.5695</v>
       </c>
       <c r="K97" s="46" t="n"/>
       <c r="L97" s="46" t="n">
-        <v>0.675</v>
+        <v>0.5002</v>
       </c>
       <c r="M97" s="46" t="n">
         <v>0.65</v>
@@ -10400,28 +10408,30 @@
       <c r="N97" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O97" s="46" t="n"/>
+      <c r="O97" s="46" t="n">
+        <v>0.0925</v>
+      </c>
       <c r="P97" s="46" t="n"/>
       <c r="Q97" s="49" t="n">
-        <v>0.5365</v>
+        <v>0.88</v>
       </c>
       <c r="R97" s="49" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S97" s="50" t="n">
-        <v>0.342</v>
+        <v>1</v>
       </c>
       <c r="T97" s="49" t="n">
-        <v>0.9911</v>
+        <v>0.9918</v>
       </c>
       <c r="U97" s="49" t="n">
-        <v>0.4601</v>
+        <v>0.6556</v>
       </c>
       <c r="V97" s="49" t="n">
-        <v>0.1965</v>
+        <v>0.5709</v>
       </c>
       <c r="W97" s="49" t="n">
-        <v>0.625</v>
+        <v>0.825</v>
       </c>
       <c r="X97" s="49" t="inlineStr">
         <is>
@@ -10433,10 +10443,10 @@
         <v>0</v>
       </c>
       <c r="AA97" s="46" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="AB97" s="46" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="AB97" s="51" t="n">
+        <v>0.867</v>
       </c>
       <c r="AC97" s="46" t="inlineStr">
         <is>
@@ -10444,13 +10454,13 @@
         </is>
       </c>
       <c r="AD97" s="46" t="n">
-        <v>0.359</v>
+        <v>0.175</v>
       </c>
       <c r="AE97" s="46" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AF97" s="46" t="n">
-        <v>0.197</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
@@ -10459,38 +10469,38 @@
       </c>
       <c r="B98" s="47" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C98" s="58" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="D98" s="58" t="n">
-        <v>0.64</v>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C98" s="59" t="inlineStr">
+        <is>
+          <t>Insulated</t>
+        </is>
+      </c>
+      <c r="D98" s="59" t="n">
+        <v>0.649</v>
       </c>
       <c r="E98" s="46" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6495</v>
       </c>
       <c r="F98" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>1.00 (&gt;180d)</t>
         </is>
       </c>
       <c r="G98" s="46" t="n"/>
       <c r="H98" s="46" t="n">
-        <v>0.7534</v>
+        <v>0.6812</v>
       </c>
       <c r="I98" s="46" t="n">
-        <v>0.876</v>
+        <v>0.8151</v>
       </c>
       <c r="J98" s="46" t="n">
-        <v>0.5695</v>
+        <v>0.4804</v>
       </c>
       <c r="K98" s="46" t="n"/>
       <c r="L98" s="46" t="n">
-        <v>0.5002</v>
+        <v>0.675</v>
       </c>
       <c r="M98" s="46" t="n">
         <v>0.65</v>
@@ -10498,30 +10508,28 @@
       <c r="N98" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O98" s="46" t="n">
-        <v>0.0925</v>
-      </c>
+      <c r="O98" s="46" t="n"/>
       <c r="P98" s="46" t="n"/>
       <c r="Q98" s="49" t="n">
-        <v>0.88</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="R98" s="49" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="S98" s="50" t="n">
-        <v>1</v>
+        <v>0.283</v>
       </c>
       <c r="T98" s="49" t="n">
-        <v>0.9918</v>
+        <v>0.9823</v>
       </c>
       <c r="U98" s="49" t="n">
-        <v>0.6556</v>
+        <v>0.77</v>
       </c>
       <c r="V98" s="49" t="n">
-        <v>0.5709</v>
+        <v>0.3492</v>
       </c>
       <c r="W98" s="49" t="n">
-        <v>0.825</v>
+        <v>0.775</v>
       </c>
       <c r="X98" s="49" t="inlineStr">
         <is>
@@ -10533,24 +10541,24 @@
         <v>0</v>
       </c>
       <c r="AA98" s="46" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AB98" s="51" t="n">
-        <v>0.867</v>
+        <v>0.84</v>
+      </c>
+      <c r="AB98" s="46" t="n">
+        <v>0.413</v>
       </c>
       <c r="AC98" s="46" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.5707</t>
         </is>
       </c>
       <c r="AD98" s="46" t="n">
-        <v>0.175</v>
+        <v>0.124</v>
       </c>
       <c r="AE98" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF98" s="46" t="n">
-        <v>0.571</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
@@ -10559,7 +10567,7 @@
       </c>
       <c r="B99" s="47" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C99" s="59" t="inlineStr">
@@ -10568,10 +10576,10 @@
         </is>
       </c>
       <c r="D99" s="59" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="E99" s="46" t="n">
-        <v>0.7156</v>
+        <v>0.7206</v>
       </c>
       <c r="F99" s="46" t="inlineStr">
         <is>
@@ -10580,61 +10588,63 @@
       </c>
       <c r="G99" s="46" t="n"/>
       <c r="H99" s="46" t="n">
-        <v>0.7298</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="I99" s="46" t="n">
-        <v>0.832</v>
+        <v>0.855</v>
       </c>
       <c r="J99" s="46" t="n">
-        <v>0.5765</v>
+        <v>0.4954</v>
       </c>
       <c r="K99" s="46" t="n"/>
       <c r="L99" s="46" t="n">
-        <v>0.675</v>
+        <v>0.6984</v>
       </c>
       <c r="M99" s="46" t="n">
-        <v>0.65</v>
+        <v>0.911</v>
       </c>
       <c r="N99" s="46" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O99" s="46" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="O99" s="46" t="n">
+        <v>0.0985</v>
+      </c>
       <c r="P99" s="46" t="n"/>
       <c r="Q99" s="49" t="n">
-        <v>0.742</v>
+        <v>0.7521</v>
       </c>
       <c r="R99" s="49" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="S99" s="50" t="n">
-        <v>1</v>
+        <v>0.659</v>
       </c>
       <c r="T99" s="49" t="n">
-        <v>0.9641</v>
+        <v>0.6415</v>
       </c>
       <c r="U99" s="49" t="n">
-        <v>0.626</v>
+        <v>0.7451</v>
       </c>
       <c r="V99" s="49" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.8648</v>
       </c>
       <c r="W99" s="49" t="n">
-        <v>0.625</v>
+        <v>0.475</v>
       </c>
       <c r="X99" s="49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y99" s="46" t="n"/>
       <c r="Z99" s="46" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AA99" s="46" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="AB99" s="46" t="n">
-        <v>0.003</v>
+        <v>0.498</v>
+      </c>
+      <c r="AB99" s="51" t="n">
+        <v>0.733</v>
       </c>
       <c r="AC99" s="46" t="inlineStr">
         <is>
@@ -10642,13 +10652,13 @@
         </is>
       </c>
       <c r="AD99" s="46" t="n">
-        <v>0.293</v>
+        <v>0.415</v>
       </c>
       <c r="AE99" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF99" s="46" t="n">
-        <v>0.74</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -10657,7 +10667,7 @@
       </c>
       <c r="B100" s="47" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C100" s="59" t="inlineStr">
@@ -10666,29 +10676,29 @@
         </is>
       </c>
       <c r="D100" s="59" t="n">
-        <v>0.646</v>
+        <v>0.655</v>
       </c>
       <c r="E100" s="46" t="n">
-        <v>0.7179</v>
+        <v>0.655</v>
       </c>
       <c r="F100" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>1.00 (&gt;180d)</t>
         </is>
       </c>
       <c r="G100" s="46" t="n"/>
       <c r="H100" s="46" t="n">
-        <v>0.7784</v>
+        <v>0.7463</v>
       </c>
       <c r="I100" s="46" t="n">
-        <v>0.919</v>
+        <v>0.845</v>
       </c>
       <c r="J100" s="46" t="n">
-        <v>0.5676</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="K100" s="46" t="n"/>
       <c r="L100" s="46" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="M100" s="46" t="n">
         <v>0.65</v>
@@ -10696,28 +10706,30 @@
       <c r="N100" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O100" s="46" t="n"/>
+      <c r="O100" s="46" t="n">
+        <v>0.0677</v>
+      </c>
       <c r="P100" s="46" t="n"/>
       <c r="Q100" s="49" t="n">
-        <v>0.7002</v>
+        <v>0.7259</v>
       </c>
       <c r="R100" s="49" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="S100" s="50" t="n">
-        <v>0.66</v>
+        <v>0.575</v>
       </c>
       <c r="T100" s="49" t="n">
-        <v>0.963</v>
+        <v>0.9585</v>
       </c>
       <c r="U100" s="49" t="n">
-        <v>0.8247</v>
+        <v>0.8931</v>
       </c>
       <c r="V100" s="49" t="n">
-        <v>0.6814</v>
+        <v>0.7028</v>
       </c>
       <c r="W100" s="49" t="n">
-        <v>0.675</v>
+        <v>0.7</v>
       </c>
       <c r="X100" s="49" t="inlineStr">
         <is>
@@ -10729,24 +10741,24 @@
         <v>0</v>
       </c>
       <c r="AA100" s="46" t="n">
-        <v>0.912</v>
+        <v>0.923</v>
       </c>
       <c r="AB100" s="46" t="n">
-        <v>0.575</v>
+        <v>0.44</v>
       </c>
       <c r="AC100" s="46" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.6265</t>
         </is>
       </c>
       <c r="AD100" s="46" t="n">
-        <v>0.212</v>
+        <v>0.305</v>
       </c>
       <c r="AE100" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF100" s="46" t="n">
-        <v>0.681</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -10755,7 +10767,7 @@
       </c>
       <c r="B101" s="47" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C101" s="59" t="inlineStr">
@@ -10764,29 +10776,29 @@
         </is>
       </c>
       <c r="D101" s="59" t="n">
-        <v>0.649</v>
+        <v>0.664</v>
       </c>
       <c r="E101" s="46" t="n">
-        <v>0.6495</v>
+        <v>0.7377</v>
       </c>
       <c r="F101" s="46" t="inlineStr">
         <is>
-          <t>1.00 (&gt;180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G101" s="46" t="n"/>
       <c r="H101" s="46" t="n">
-        <v>0.6812</v>
+        <v>0.7153</v>
       </c>
       <c r="I101" s="46" t="n">
-        <v>0.8151</v>
+        <v>0.8175</v>
       </c>
       <c r="J101" s="46" t="n">
-        <v>0.4804</v>
+        <v>0.5619</v>
       </c>
       <c r="K101" s="46" t="n"/>
       <c r="L101" s="46" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="M101" s="46" t="n">
         <v>0.65</v>
@@ -10794,28 +10806,30 @@
       <c r="N101" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O101" s="46" t="n"/>
+      <c r="O101" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P101" s="46" t="n"/>
       <c r="Q101" s="49" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.7252</v>
       </c>
       <c r="R101" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S101" s="50" t="n">
-        <v>0.283</v>
+        <v>1</v>
       </c>
       <c r="T101" s="49" t="n">
-        <v>0.9823</v>
+        <v>0.9782</v>
       </c>
       <c r="U101" s="49" t="n">
-        <v>0.77</v>
+        <v>0.5567</v>
       </c>
       <c r="V101" s="49" t="n">
-        <v>0.3492</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="W101" s="49" t="n">
-        <v>0.775</v>
+        <v>0.575</v>
       </c>
       <c r="X101" s="49" t="inlineStr">
         <is>
@@ -10827,24 +10841,24 @@
         <v>0</v>
       </c>
       <c r="AA101" s="46" t="n">
-        <v>0.84</v>
+        <v>0.833</v>
       </c>
       <c r="AB101" s="46" t="n">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="46" t="inlineStr">
         <is>
-          <t>0.5707</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD101" s="46" t="n">
-        <v>0.124</v>
+        <v>0.316</v>
       </c>
       <c r="AE101" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF101" s="46" t="n">
-        <v>0.349</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
@@ -10853,7 +10867,7 @@
       </c>
       <c r="B102" s="47" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C102" s="59" t="inlineStr">
@@ -10862,75 +10876,73 @@
         </is>
       </c>
       <c r="D102" s="59" t="n">
-        <v>0.649</v>
+        <v>0.667</v>
       </c>
       <c r="E102" s="46" t="n">
-        <v>0.7206</v>
+        <v>0.6671</v>
       </c>
       <c r="F102" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>1.00 (&gt;180d)</t>
         </is>
       </c>
       <c r="G102" s="46" t="n"/>
       <c r="H102" s="46" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.709</v>
       </c>
       <c r="I102" s="46" t="n">
-        <v>0.855</v>
+        <v>0.823</v>
       </c>
       <c r="J102" s="46" t="n">
-        <v>0.4954</v>
+        <v>0.538</v>
       </c>
       <c r="K102" s="46" t="n"/>
       <c r="L102" s="46" t="n">
-        <v>0.6984</v>
+        <v>0.675</v>
       </c>
       <c r="M102" s="46" t="n">
-        <v>0.911</v>
+        <v>0.65</v>
       </c>
       <c r="N102" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O102" s="46" t="n">
-        <v>0.0985</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="O102" s="46" t="n"/>
       <c r="P102" s="46" t="n"/>
       <c r="Q102" s="49" t="n">
-        <v>0.7521</v>
+        <v>0.6173</v>
       </c>
       <c r="R102" s="49" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="S102" s="50" t="n">
-        <v>0.659</v>
+        <v>0.192</v>
       </c>
       <c r="T102" s="49" t="n">
-        <v>0.6415</v>
+        <v>0.9845</v>
       </c>
       <c r="U102" s="49" t="n">
-        <v>0.7451</v>
+        <v>0.8766</v>
       </c>
       <c r="V102" s="49" t="n">
-        <v>0.8648</v>
+        <v>0.6796</v>
       </c>
       <c r="W102" s="49" t="n">
-        <v>0.475</v>
+        <v>0.65</v>
       </c>
       <c r="X102" s="49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="Y102" s="46" t="n"/>
       <c r="Z102" s="46" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AA102" s="46" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="AB102" s="51" t="n">
-        <v>0.733</v>
+        <v>0.632</v>
+      </c>
+      <c r="AB102" s="46" t="n">
+        <v>0.313</v>
       </c>
       <c r="AC102" s="46" t="inlineStr">
         <is>
@@ -10938,13 +10950,13 @@
         </is>
       </c>
       <c r="AD102" s="46" t="n">
-        <v>0.415</v>
+        <v>0.388</v>
       </c>
       <c r="AE102" s="46" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF102" s="46" t="n">
-        <v>0.865</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
@@ -10953,7 +10965,7 @@
       </c>
       <c r="B103" s="47" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C103" s="59" t="inlineStr">
@@ -10962,10 +10974,10 @@
         </is>
       </c>
       <c r="D103" s="59" t="n">
-        <v>0.661</v>
+        <v>0.673</v>
       </c>
       <c r="E103" s="46" t="n">
-        <v>0.7347</v>
+        <v>0.7481</v>
       </c>
       <c r="F103" s="46" t="inlineStr">
         <is>
@@ -10974,24 +10986,30 @@
       </c>
       <c r="G103" s="46" t="n"/>
       <c r="H103" s="46" t="n">
-        <v>0.7733</v>
+        <v>0.7298</v>
       </c>
       <c r="I103" s="46" t="n">
-        <v>0.9155</v>
+        <v>0.832</v>
       </c>
       <c r="J103" s="46" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5765</v>
       </c>
       <c r="K103" s="46" t="n"/>
       <c r="L103" s="46" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="M103" s="46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N103" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="M103" s="46" t="n"/>
-      <c r="N103" s="46" t="n"/>
-      <c r="O103" s="46" t="n"/>
+      <c r="O103" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P103" s="46" t="n"/>
       <c r="Q103" s="49" t="n">
-        <v>0.7309</v>
+        <v>0.742</v>
       </c>
       <c r="R103" s="49" t="n">
         <v>0.5</v>
@@ -11000,16 +11018,16 @@
         <v>1</v>
       </c>
       <c r="T103" s="49" t="n">
-        <v>0.9581</v>
+        <v>0.9641</v>
       </c>
       <c r="U103" s="49" t="n">
-        <v>0.6807</v>
+        <v>0.626</v>
       </c>
       <c r="V103" s="49" t="n">
-        <v>0.6341</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="W103" s="49" t="n">
-        <v>0.475</v>
+        <v>0.625</v>
       </c>
       <c r="X103" s="49" t="inlineStr">
         <is>
@@ -11021,10 +11039,10 @@
         <v>0</v>
       </c>
       <c r="AA103" s="46" t="n">
-        <v>0.907</v>
+        <v>0.904</v>
       </c>
       <c r="AB103" s="46" t="n">
-        <v>0.554</v>
+        <v>0.003</v>
       </c>
       <c r="AC103" s="46" t="inlineStr">
         <is>
@@ -11032,13 +11050,13 @@
         </is>
       </c>
       <c r="AD103" s="46" t="n">
-        <v>0.345</v>
+        <v>0.293</v>
       </c>
       <c r="AE103" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF103" s="46" t="n">
-        <v>0.634</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
@@ -11047,7 +11065,7 @@
       </c>
       <c r="B104" s="47" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C104" s="59" t="inlineStr">
@@ -11056,10 +11074,10 @@
         </is>
       </c>
       <c r="D104" s="59" t="n">
-        <v>0.662</v>
+        <v>0.675</v>
       </c>
       <c r="E104" s="46" t="n">
-        <v>0.736</v>
+        <v>0.7504</v>
       </c>
       <c r="F104" s="46" t="inlineStr">
         <is>
@@ -11068,17 +11086,17 @@
       </c>
       <c r="G104" s="46" t="n"/>
       <c r="H104" s="46" t="n">
-        <v>0.7859</v>
+        <v>0.7784</v>
       </c>
       <c r="I104" s="46" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="J104" s="46" t="n">
-        <v>0.5833</v>
+        <v>0.5676</v>
       </c>
       <c r="K104" s="46" t="n"/>
       <c r="L104" s="46" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="M104" s="46" t="n">
         <v>0.65</v>
@@ -11086,28 +11104,30 @@
       <c r="N104" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O104" s="46" t="n"/>
+      <c r="O104" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P104" s="46" t="n"/>
       <c r="Q104" s="49" t="n">
-        <v>0.7471</v>
+        <v>0.7002</v>
       </c>
       <c r="R104" s="49" t="n">
         <v>0.5</v>
       </c>
       <c r="S104" s="50" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="T104" s="49" t="n">
-        <v>0.9828</v>
+        <v>0.963</v>
       </c>
       <c r="U104" s="49" t="n">
-        <v>0.6959</v>
+        <v>0.8247</v>
       </c>
       <c r="V104" s="49" t="n">
-        <v>0.6987</v>
+        <v>0.6814</v>
       </c>
       <c r="W104" s="49" t="n">
-        <v>0.525</v>
+        <v>0.675</v>
       </c>
       <c r="X104" s="49" t="inlineStr">
         <is>
@@ -11119,10 +11139,10 @@
         <v>0</v>
       </c>
       <c r="AA104" s="46" t="n">
-        <v>0.887</v>
+        <v>0.912</v>
       </c>
       <c r="AB104" s="46" t="n">
-        <v>0.614</v>
+        <v>0.575</v>
       </c>
       <c r="AC104" s="46" t="inlineStr">
         <is>
@@ -11130,22 +11150,22 @@
         </is>
       </c>
       <c r="AD104" s="46" t="n">
-        <v>0.297</v>
+        <v>0.212</v>
       </c>
       <c r="AE104" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF104" s="46" t="n">
-        <v>0.699</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="46" t="n">
+      <c r="A105" s="60" t="n">
         <v>102</v>
       </c>
-      <c r="B105" s="47" t="inlineStr">
-        <is>
-          <t>Portugal</t>
+      <c r="B105" s="61" t="inlineStr">
+        <is>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C105" s="59" t="inlineStr">
@@ -11154,96 +11174,82 @@
         </is>
       </c>
       <c r="D105" s="59" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="E105" s="46" t="n">
-        <v>0.6671</v>
-      </c>
-      <c r="F105" s="46" t="inlineStr">
-        <is>
-          <t>1.00 (&gt;180d)</t>
-        </is>
-      </c>
-      <c r="G105" s="46" t="n"/>
-      <c r="H105" s="46" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="I105" s="46" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="J105" s="46" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="K105" s="46" t="n"/>
-      <c r="L105" s="46" t="n">
         <v>0.675</v>
       </c>
-      <c r="M105" s="46" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N105" s="46" t="n">
+      <c r="E105" s="60" t="n">
+        <v>0.7504</v>
+      </c>
+      <c r="F105" s="60" t="inlineStr">
+        <is>
+          <t>0.90 (30-90d)</t>
+        </is>
+      </c>
+      <c r="G105" s="60" t="n"/>
+      <c r="H105" s="60" t="n">
+        <v>0.8007</v>
+      </c>
+      <c r="I105" s="60" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="J105" s="60" t="n">
+        <v>0.5911</v>
+      </c>
+      <c r="K105" s="60" t="n"/>
+      <c r="L105" s="60" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="M105" s="60" t="n"/>
+      <c r="N105" s="60" t="n">
         <v>0.7</v>
       </c>
-      <c r="O105" s="46" t="n"/>
-      <c r="P105" s="46" t="n"/>
-      <c r="Q105" s="49" t="n">
-        <v>0.6173</v>
-      </c>
-      <c r="R105" s="49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S105" s="50" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="T105" s="49" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="U105" s="49" t="n">
-        <v>0.8766</v>
-      </c>
-      <c r="V105" s="49" t="n">
-        <v>0.6796</v>
-      </c>
-      <c r="W105" s="49" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="X105" s="49" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="Y105" s="46" t="n"/>
-      <c r="Z105" s="46" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AA105" s="46" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AB105" s="46" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="AC105" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="AD105" s="46" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="AE105" s="46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF105" s="46" t="n">
-        <v>0.68</v>
+      <c r="O105" s="60" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="P105" s="60" t="n"/>
+      <c r="Q105" s="60" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="R105" s="60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S105" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="60" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="U105" s="60" t="n">
+        <v>0.6054</v>
+      </c>
+      <c r="V105" s="60" t="n">
+        <v>0.9187</v>
+      </c>
+      <c r="W105" s="60" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="X105" s="60" t="n"/>
+      <c r="Y105" s="60" t="n"/>
+      <c r="Z105" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="60" t="n"/>
+      <c r="AB105" s="60" t="n"/>
+      <c r="AC105" s="60" t="n"/>
+      <c r="AD105" s="60" t="n"/>
+      <c r="AE105" s="60" t="n"/>
+      <c r="AF105" s="60" t="inlineStr">
+        <is>
+          <t>★ ANNOTATED — FX excluded. HIC floor 0.70.</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="46" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106" s="47" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C106" s="59" t="inlineStr">
@@ -11252,29 +11258,29 @@
         </is>
       </c>
       <c r="D106" s="59" t="n">
-        <v>0.671</v>
+        <v>0.678</v>
       </c>
       <c r="E106" s="46" t="n">
-        <v>0.7458</v>
+        <v>0.714</v>
       </c>
       <c r="F106" s="46" t="inlineStr">
         <is>
-          <t>0.90 (30-90d)</t>
+          <t>0.95 (90-180d)</t>
         </is>
       </c>
       <c r="G106" s="46" t="n"/>
       <c r="H106" s="46" t="n">
-        <v>0.7701</v>
+        <v>0.6857</v>
       </c>
       <c r="I106" s="46" t="n">
-        <v>0.9075</v>
+        <v>0.743</v>
       </c>
       <c r="J106" s="46" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5998</v>
       </c>
       <c r="K106" s="46" t="n"/>
       <c r="L106" s="46" t="n">
-        <v>0.675</v>
+        <v>0.6515</v>
       </c>
       <c r="M106" s="46" t="n">
         <v>0.65</v>
@@ -11282,28 +11288,30 @@
       <c r="N106" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O106" s="46" t="n"/>
+      <c r="O106" s="46" t="n">
+        <v>0.5968</v>
+      </c>
       <c r="P106" s="46" t="n"/>
       <c r="Q106" s="49" t="n">
-        <v>0.7924</v>
+        <v>0.8048</v>
       </c>
       <c r="R106" s="49" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="S106" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T106" s="49" t="n">
-        <v>0.9529</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="U106" s="49" t="n">
-        <v>0.6185</v>
+        <v>0.6631</v>
       </c>
       <c r="V106" s="49" t="n">
-        <v>0.6776</v>
+        <v>0.7017</v>
       </c>
       <c r="W106" s="49" t="n">
-        <v>0.625</v>
+        <v>0.775</v>
       </c>
       <c r="X106" s="49" t="inlineStr">
         <is>
@@ -11312,13 +11320,13 @@
       </c>
       <c r="Y106" s="46" t="n"/>
       <c r="Z106" s="46" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="AA106" s="46" t="n">
-        <v>0.913</v>
+        <v>0.91</v>
       </c>
       <c r="AB106" s="51" t="n">
-        <v>0.495</v>
+        <v>0.228</v>
       </c>
       <c r="AC106" s="46" t="inlineStr">
         <is>
@@ -11326,106 +11334,122 @@
         </is>
       </c>
       <c r="AD106" s="46" t="n">
-        <v>0.314</v>
+        <v>0.125</v>
       </c>
       <c r="AE106" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF106" s="46" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="46" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C107" s="59" t="inlineStr">
+        <is>
+          <t>Insulated</t>
+        </is>
+      </c>
+      <c r="D107" s="59" t="n">
         <v>0.678</v>
       </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="60" t="n">
-        <v>104</v>
-      </c>
-      <c r="B107" s="61" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="C107" s="59" t="inlineStr">
-        <is>
-          <t>Insulated</t>
-        </is>
-      </c>
-      <c r="D107" s="59" t="n">
+      <c r="E107" s="46" t="n">
+        <v>0.6783</v>
+      </c>
+      <c r="F107" s="46" t="inlineStr">
+        <is>
+          <t>1.00 (&gt;180d)</t>
+        </is>
+      </c>
+      <c r="G107" s="46" t="n"/>
+      <c r="H107" s="46" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+      <c r="I107" s="46" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="J107" s="46" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="K107" s="46" t="n"/>
+      <c r="L107" s="46" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="M107" s="46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N107" s="46" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O107" s="46" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="P107" s="46" t="n"/>
+      <c r="Q107" s="49" t="n">
+        <v>0.7722</v>
+      </c>
+      <c r="R107" s="49" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S107" s="50" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="T107" s="49" t="n">
+        <v>0.9823</v>
+      </c>
+      <c r="U107" s="49" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="V107" s="49" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="W107" s="49" t="n">
         <v>0.675</v>
       </c>
-      <c r="E107" s="60" t="n">
-        <v>0.7504</v>
-      </c>
-      <c r="F107" s="60" t="inlineStr">
-        <is>
-          <t>0.90 (30-90d)</t>
-        </is>
-      </c>
-      <c r="G107" s="60" t="n"/>
-      <c r="H107" s="60" t="n">
-        <v>0.8007</v>
-      </c>
-      <c r="I107" s="60" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="J107" s="60" t="n">
-        <v>0.5911</v>
-      </c>
-      <c r="K107" s="60" t="n"/>
-      <c r="L107" s="60" t="n">
-        <v>0.5769</v>
-      </c>
-      <c r="M107" s="60" t="n"/>
-      <c r="N107" s="60" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O107" s="60" t="n">
-        <v>0.4333</v>
-      </c>
-      <c r="P107" s="60" t="n"/>
-      <c r="Q107" s="60" t="n">
-        <v>0.8735000000000001</v>
-      </c>
-      <c r="R107" s="60" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S107" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" s="60" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="U107" s="60" t="n">
-        <v>0.6054</v>
-      </c>
-      <c r="V107" s="60" t="n">
-        <v>0.9187</v>
-      </c>
-      <c r="W107" s="60" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="X107" s="60" t="n"/>
-      <c r="Y107" s="60" t="n"/>
-      <c r="Z107" s="60" t="n">
+      <c r="X107" s="49" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Y107" s="46" t="n"/>
+      <c r="Z107" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AA107" s="60" t="n"/>
-      <c r="AB107" s="60" t="n"/>
-      <c r="AC107" s="60" t="n"/>
-      <c r="AD107" s="60" t="n"/>
-      <c r="AE107" s="60" t="n"/>
-      <c r="AF107" s="60" t="inlineStr">
-        <is>
-          <t>★ ANNOTATED — FX excluded. HIC floor 0.70.</t>
-        </is>
+      <c r="AA107" s="46" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="AB107" s="51" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AC107" s="46" t="inlineStr">
+        <is>
+          <t>0.8830</t>
+        </is>
+      </c>
+      <c r="AD107" s="46" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="AE107" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF107" s="46" t="n">
+        <v>0.481</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="46" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" s="47" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C108" s="59" t="inlineStr">
@@ -11437,57 +11461,57 @@
         <v>0.678</v>
       </c>
       <c r="E108" s="46" t="n">
-        <v>0.714</v>
+        <v>0.6785</v>
       </c>
       <c r="F108" s="46" t="inlineStr">
         <is>
-          <t>0.95 (90-180d)</t>
+          <t>1.00 (&gt;180d)</t>
         </is>
       </c>
       <c r="G108" s="46" t="n"/>
       <c r="H108" s="46" t="n">
-        <v>0.6857</v>
+        <v>0.7318</v>
       </c>
       <c r="I108" s="46" t="n">
-        <v>0.743</v>
+        <v>0.897</v>
       </c>
       <c r="J108" s="46" t="n">
-        <v>0.5998</v>
+        <v>0.4839</v>
       </c>
       <c r="K108" s="46" t="n"/>
       <c r="L108" s="46" t="n">
-        <v>0.6515</v>
+        <v>0.6223</v>
       </c>
       <c r="M108" s="46" t="n">
-        <v>0.65</v>
+        <v>0.7779</v>
       </c>
       <c r="N108" s="46" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O108" s="46" t="n">
-        <v>0.5968</v>
+        <v>0</v>
       </c>
       <c r="P108" s="46" t="n"/>
       <c r="Q108" s="49" t="n">
-        <v>0.8048</v>
+        <v>0.6815</v>
       </c>
       <c r="R108" s="49" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="S108" s="50" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="T108" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="T108" s="49" t="n">
-        <v>0.6022999999999999</v>
-      </c>
       <c r="U108" s="49" t="n">
-        <v>0.6631</v>
+        <v>0.5273</v>
       </c>
       <c r="V108" s="49" t="n">
-        <v>0.7017</v>
+        <v>0.2874</v>
       </c>
       <c r="W108" s="49" t="n">
-        <v>0.775</v>
+        <v>0.725</v>
       </c>
       <c r="X108" s="49" t="inlineStr">
         <is>
@@ -11496,13 +11520,13 @@
       </c>
       <c r="Y108" s="46" t="n"/>
       <c r="Z108" s="46" t="n">
-        <v>24.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA108" s="46" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AB108" s="51" t="n">
-        <v>0.228</v>
+        <v>0.75</v>
+      </c>
+      <c r="AB108" s="46" t="n">
+        <v>0.698</v>
       </c>
       <c r="AC108" s="46" t="inlineStr">
         <is>
@@ -11510,22 +11534,22 @@
         </is>
       </c>
       <c r="AD108" s="46" t="n">
-        <v>0.125</v>
+        <v>0.169</v>
       </c>
       <c r="AE108" s="46" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AF108" s="46" t="n">
-        <v>0.702</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="46" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B109" s="47" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C109" s="59" t="inlineStr">
@@ -11534,29 +11558,29 @@
         </is>
       </c>
       <c r="D109" s="59" t="n">
-        <v>0.678</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E109" s="46" t="n">
-        <v>0.6783</v>
+        <v>0.7589</v>
       </c>
       <c r="F109" s="46" t="inlineStr">
         <is>
-          <t>1.00 (&gt;180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G109" s="46" t="n"/>
       <c r="H109" s="46" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="I109" s="46" t="n">
-        <v>0.859</v>
+        <v>0.9155</v>
       </c>
       <c r="J109" s="46" t="n">
-        <v>0.5476</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K109" s="46" t="n"/>
       <c r="L109" s="46" t="n">
-        <v>0.5282</v>
+        <v>0.7725</v>
       </c>
       <c r="M109" s="46" t="n">
         <v>0.65</v>
@@ -11565,29 +11589,29 @@
         <v>0.7</v>
       </c>
       <c r="O109" s="46" t="n">
-        <v>0.1855</v>
+        <v>1</v>
       </c>
       <c r="P109" s="46" t="n"/>
       <c r="Q109" s="49" t="n">
-        <v>0.7722</v>
+        <v>0.7309</v>
       </c>
       <c r="R109" s="49" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="S109" s="50" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
       <c r="T109" s="49" t="n">
-        <v>0.9823</v>
+        <v>0.9581</v>
       </c>
       <c r="U109" s="49" t="n">
-        <v>0.6369</v>
+        <v>0.6807</v>
       </c>
       <c r="V109" s="49" t="n">
-        <v>0.4809</v>
+        <v>0.6341</v>
       </c>
       <c r="W109" s="49" t="n">
-        <v>0.675</v>
+        <v>0.475</v>
       </c>
       <c r="X109" s="49" t="inlineStr">
         <is>
@@ -11599,24 +11623,24 @@
         <v>0</v>
       </c>
       <c r="AA109" s="46" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="AB109" s="51" t="n">
-        <v>0.287</v>
+        <v>0.907</v>
+      </c>
+      <c r="AB109" s="46" t="n">
+        <v>0.554</v>
       </c>
       <c r="AC109" s="46" t="inlineStr">
         <is>
-          <t>0.8830</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD109" s="46" t="n">
-        <v>0.168</v>
+        <v>0.345</v>
       </c>
       <c r="AE109" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF109" s="46" t="n">
-        <v>0.481</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -11625,7 +11649,7 @@
       </c>
       <c r="B110" s="47" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C110" s="59" t="inlineStr">
@@ -11634,10 +11658,10 @@
         </is>
       </c>
       <c r="D110" s="59" t="n">
-        <v>0.678</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E110" s="46" t="n">
-        <v>0.6785</v>
+        <v>0.6891</v>
       </c>
       <c r="F110" s="46" t="inlineStr">
         <is>
@@ -11646,48 +11670,46 @@
       </c>
       <c r="G110" s="46" t="n"/>
       <c r="H110" s="46" t="n">
-        <v>0.7318</v>
+        <v>0.755</v>
       </c>
       <c r="I110" s="46" t="n">
-        <v>0.897</v>
+        <v>0.827</v>
       </c>
       <c r="J110" s="46" t="n">
-        <v>0.4839</v>
+        <v>0.647</v>
       </c>
       <c r="K110" s="46" t="n"/>
       <c r="L110" s="46" t="n">
-        <v>0.6223</v>
+        <v>0.675</v>
       </c>
       <c r="M110" s="46" t="n">
-        <v>0.7779</v>
+        <v>0.65</v>
       </c>
       <c r="N110" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O110" s="46" t="n">
-        <v>0</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="O110" s="46" t="n"/>
       <c r="P110" s="46" t="n"/>
       <c r="Q110" s="49" t="n">
-        <v>0.6815</v>
+        <v>0.6372</v>
       </c>
       <c r="R110" s="49" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="S110" s="50" t="n">
-        <v>0.217</v>
+        <v>0.097</v>
       </c>
       <c r="T110" s="49" t="n">
-        <v>1</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="U110" s="49" t="n">
-        <v>0.5273</v>
+        <v>0.74</v>
       </c>
       <c r="V110" s="49" t="n">
-        <v>0.2874</v>
+        <v>0.6937</v>
       </c>
       <c r="W110" s="49" t="n">
-        <v>0.725</v>
+        <v>0.8</v>
       </c>
       <c r="X110" s="49" t="inlineStr">
         <is>
@@ -11696,27 +11718,27 @@
       </c>
       <c r="Y110" s="46" t="n"/>
       <c r="Z110" s="46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA110" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB110" s="46" t="n">
-        <v>0.698</v>
+        <v>0.843</v>
+      </c>
+      <c r="AB110" s="51" t="n">
+        <v>0.122</v>
       </c>
       <c r="AC110" s="46" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.9350</t>
         </is>
       </c>
       <c r="AD110" s="46" t="n">
-        <v>0.169</v>
+        <v>0.047</v>
       </c>
       <c r="AE110" s="46" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="AF110" s="46" t="n">
-        <v>0.287</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
@@ -11725,7 +11747,7 @@
       </c>
       <c r="B111" s="47" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C111" s="59" t="inlineStr">
@@ -11734,10 +11756,10 @@
         </is>
       </c>
       <c r="D111" s="59" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E111" s="46" t="n">
-        <v>0.7617</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F111" s="46" t="inlineStr">
         <is>
@@ -11746,20 +11768,20 @@
       </c>
       <c r="G111" s="46" t="n"/>
       <c r="H111" s="46" t="n">
-        <v>0.7104</v>
+        <v>0.7338</v>
       </c>
       <c r="I111" s="46" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8495</v>
       </c>
       <c r="J111" s="46" t="n">
-        <v>0.5596</v>
+        <v>0.5602</v>
       </c>
       <c r="K111" s="46" t="n"/>
       <c r="L111" s="46" t="n">
-        <v>0.774</v>
+        <v>0.85</v>
       </c>
       <c r="M111" s="46" t="n">
-        <v>0.8481</v>
+        <v>1</v>
       </c>
       <c r="N111" s="46" t="n">
         <v>0.7</v>
@@ -11767,22 +11789,22 @@
       <c r="O111" s="46" t="n"/>
       <c r="P111" s="46" t="n"/>
       <c r="Q111" s="49" t="n">
-        <v>0.8007</v>
+        <v>0.7159</v>
       </c>
       <c r="R111" s="49" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="S111" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T111" s="49" t="n">
-        <v>0.9587</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="U111" s="49" t="n">
-        <v>0.6647</v>
+        <v>0.6503</v>
       </c>
       <c r="V111" s="49" t="n">
-        <v>0.6954</v>
+        <v>0.6109</v>
       </c>
       <c r="W111" s="49" t="n">
         <v>0.475</v>
@@ -11797,22 +11819,24 @@
         <v>0</v>
       </c>
       <c r="AA111" s="46" t="n">
-        <v>0.924</v>
+        <v>0.852</v>
       </c>
       <c r="AB111" s="46" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="AC111" s="46" t="n">
-        <v>0.72</v>
+        <v>0.197</v>
+      </c>
+      <c r="AC111" s="46" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
       </c>
       <c r="AD111" s="46" t="n">
-        <v>0.478</v>
+        <v>0.273</v>
       </c>
       <c r="AE111" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF111" s="46" t="n">
-        <v>0.695</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
@@ -11821,7 +11845,7 @@
       </c>
       <c r="B112" s="47" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C112" s="59" t="inlineStr">
@@ -11830,29 +11854,29 @@
         </is>
       </c>
       <c r="D112" s="59" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E112" s="46" t="n">
-        <v>0.6891</v>
+        <v>0.7685</v>
       </c>
       <c r="F112" s="46" t="inlineStr">
         <is>
-          <t>1.00 (&gt;180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G112" s="46" t="n"/>
       <c r="H112" s="46" t="n">
-        <v>0.755</v>
+        <v>0.7859</v>
       </c>
       <c r="I112" s="46" t="n">
-        <v>0.827</v>
+        <v>0.921</v>
       </c>
       <c r="J112" s="46" t="n">
-        <v>0.647</v>
+        <v>0.5833</v>
       </c>
       <c r="K112" s="46" t="n"/>
       <c r="L112" s="46" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="M112" s="46" t="n">
         <v>0.65</v>
@@ -11860,28 +11884,30 @@
       <c r="N112" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O112" s="46" t="n"/>
+      <c r="O112" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P112" s="46" t="n"/>
       <c r="Q112" s="49" t="n">
-        <v>0.6372</v>
+        <v>0.7471</v>
       </c>
       <c r="R112" s="49" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="S112" s="50" t="n">
-        <v>0.097</v>
+        <v>1</v>
       </c>
       <c r="T112" s="49" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9828</v>
       </c>
       <c r="U112" s="49" t="n">
-        <v>0.74</v>
+        <v>0.6959</v>
       </c>
       <c r="V112" s="49" t="n">
-        <v>0.6937</v>
+        <v>0.6987</v>
       </c>
       <c r="W112" s="49" t="n">
-        <v>0.8</v>
+        <v>0.525</v>
       </c>
       <c r="X112" s="49" t="inlineStr">
         <is>
@@ -11893,24 +11919,24 @@
         <v>0</v>
       </c>
       <c r="AA112" s="46" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="AB112" s="51" t="n">
-        <v>0.122</v>
+        <v>0.887</v>
+      </c>
+      <c r="AB112" s="46" t="n">
+        <v>0.614</v>
       </c>
       <c r="AC112" s="46" t="inlineStr">
         <is>
-          <t>0.9350</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD112" s="46" t="n">
-        <v>0.047</v>
+        <v>0.297</v>
       </c>
       <c r="AE112" s="46" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AF112" s="46" t="n">
-        <v>0.677</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
@@ -11919,7 +11945,7 @@
       </c>
       <c r="B113" s="47" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C113" s="59" t="inlineStr">
@@ -11928,10 +11954,10 @@
         </is>
       </c>
       <c r="D113" s="59" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E113" s="46" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7783</v>
       </c>
       <c r="F113" s="46" t="inlineStr">
         <is>
@@ -11940,46 +11966,48 @@
       </c>
       <c r="G113" s="46" t="n"/>
       <c r="H113" s="46" t="n">
-        <v>0.7338</v>
+        <v>0.7701</v>
       </c>
       <c r="I113" s="46" t="n">
-        <v>0.8495</v>
+        <v>0.9075</v>
       </c>
       <c r="J113" s="46" t="n">
-        <v>0.5602</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K113" s="46" t="n"/>
       <c r="L113" s="46" t="n">
-        <v>0.85</v>
+        <v>0.7725</v>
       </c>
       <c r="M113" s="46" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="N113" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O113" s="46" t="n"/>
+      <c r="O113" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P113" s="46" t="n"/>
       <c r="Q113" s="49" t="n">
-        <v>0.7159</v>
+        <v>0.7924</v>
       </c>
       <c r="R113" s="49" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="S113" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T113" s="49" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9529</v>
       </c>
       <c r="U113" s="49" t="n">
-        <v>0.6503</v>
+        <v>0.6185</v>
       </c>
       <c r="V113" s="49" t="n">
-        <v>0.6109</v>
+        <v>0.6776</v>
       </c>
       <c r="W113" s="49" t="n">
-        <v>0.475</v>
+        <v>0.625</v>
       </c>
       <c r="X113" s="49" t="inlineStr">
         <is>
@@ -11991,10 +12019,10 @@
         <v>0</v>
       </c>
       <c r="AA113" s="46" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="AB113" s="46" t="n">
-        <v>0.197</v>
+        <v>0.913</v>
+      </c>
+      <c r="AB113" s="51" t="n">
+        <v>0.495</v>
       </c>
       <c r="AC113" s="46" t="inlineStr">
         <is>
@@ -12002,13 +12030,13 @@
         </is>
       </c>
       <c r="AD113" s="46" t="n">
-        <v>0.273</v>
+        <v>0.314</v>
       </c>
       <c r="AE113" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF113" s="46" t="n">
-        <v>0.611</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
@@ -12017,7 +12045,7 @@
       </c>
       <c r="B114" s="47" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C114" s="59" t="inlineStr">
@@ -12026,10 +12054,10 @@
         </is>
       </c>
       <c r="D114" s="59" t="n">
-        <v>0.704</v>
+        <v>0.706</v>
       </c>
       <c r="E114" s="46" t="n">
-        <v>0.7825</v>
+        <v>0.7843</v>
       </c>
       <c r="F114" s="46" t="inlineStr">
         <is>
@@ -12038,46 +12066,48 @@
       </c>
       <c r="G114" s="46" t="n"/>
       <c r="H114" s="46" t="n">
-        <v>0.756</v>
+        <v>0.7104</v>
       </c>
       <c r="I114" s="46" t="n">
-        <v>0.916</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J114" s="46" t="n">
-        <v>0.5159</v>
+        <v>0.5596</v>
       </c>
       <c r="K114" s="46" t="n"/>
       <c r="L114" s="46" t="n">
-        <v>0.85</v>
+        <v>0.8418</v>
       </c>
       <c r="M114" s="46" t="n">
-        <v>1</v>
+        <v>0.8481</v>
       </c>
       <c r="N114" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O114" s="46" t="n"/>
+      <c r="O114" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P114" s="46" t="n"/>
       <c r="Q114" s="49" t="n">
-        <v>0.7415</v>
+        <v>0.8007</v>
       </c>
       <c r="R114" s="49" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="S114" s="50" t="n">
         <v>1</v>
       </c>
       <c r="T114" s="49" t="n">
-        <v>0.8963</v>
+        <v>0.9587</v>
       </c>
       <c r="U114" s="49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6647</v>
       </c>
       <c r="V114" s="49" t="n">
-        <v>0.5695</v>
+        <v>0.6954</v>
       </c>
       <c r="W114" s="49" t="n">
-        <v>0.525</v>
+        <v>0.475</v>
       </c>
       <c r="X114" s="49" t="inlineStr">
         <is>
@@ -12086,27 +12116,25 @@
       </c>
       <c r="Y114" s="46" t="n"/>
       <c r="Z114" s="46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="46" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="AB114" s="51" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="AC114" s="46" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
+        <v>0.924</v>
+      </c>
+      <c r="AB114" s="46" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AC114" s="46" t="n">
+        <v>0.72</v>
       </c>
       <c r="AD114" s="46" t="n">
-        <v>0.263</v>
+        <v>0.478</v>
       </c>
       <c r="AE114" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF114" s="46" t="n">
-        <v>0.57</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -12311,7 +12339,7 @@
       </c>
       <c r="B117" s="47" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C117" s="59" t="inlineStr">
@@ -12320,58 +12348,60 @@
         </is>
       </c>
       <c r="D117" s="59" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="E117" s="46" t="n">
-        <v>0.7157</v>
+        <v>0.7975</v>
       </c>
       <c r="F117" s="46" t="inlineStr">
         <is>
-          <t>1.00 (&gt;180d)</t>
+          <t>0.90 (30-90d)</t>
         </is>
       </c>
       <c r="G117" s="46" t="n"/>
       <c r="H117" s="46" t="n">
-        <v>0.7463</v>
+        <v>0.756</v>
       </c>
       <c r="I117" s="46" t="n">
-        <v>0.845</v>
+        <v>0.916</v>
       </c>
       <c r="J117" s="46" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5159</v>
       </c>
       <c r="K117" s="46" t="n"/>
       <c r="L117" s="46" t="n">
-        <v>0.675</v>
+        <v>0.895</v>
       </c>
       <c r="M117" s="46" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N117" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O117" s="46" t="n"/>
+      <c r="O117" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P117" s="46" t="n"/>
       <c r="Q117" s="49" t="n">
-        <v>0.7259</v>
+        <v>0.7415</v>
       </c>
       <c r="R117" s="49" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="S117" s="50" t="n">
-        <v>0.575</v>
+        <v>1</v>
       </c>
       <c r="T117" s="49" t="n">
-        <v>0.9585</v>
+        <v>0.8963</v>
       </c>
       <c r="U117" s="49" t="n">
-        <v>0.8931</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V117" s="49" t="n">
-        <v>0.7028</v>
+        <v>0.5695</v>
       </c>
       <c r="W117" s="49" t="n">
-        <v>0.7</v>
+        <v>0.525</v>
       </c>
       <c r="X117" s="49" t="inlineStr">
         <is>
@@ -12380,27 +12410,27 @@
       </c>
       <c r="Y117" s="46" t="n"/>
       <c r="Z117" s="46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA117" s="46" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AB117" s="46" t="n">
-        <v>0.44</v>
+        <v>0.908</v>
+      </c>
+      <c r="AB117" s="51" t="n">
+        <v>0.628</v>
       </c>
       <c r="AC117" s="46" t="inlineStr">
         <is>
-          <t>0.6265</t>
+          <t>1.0000</t>
         </is>
       </c>
       <c r="AD117" s="46" t="n">
-        <v>0.305</v>
+        <v>0.263</v>
       </c>
       <c r="AE117" s="46" t="n">
         <v>0.4</v>
       </c>
       <c r="AF117" s="46" t="n">
-        <v>0.703</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
@@ -12507,7 +12537,7 @@
       </c>
       <c r="B119" s="47" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C119" s="59" t="inlineStr">
@@ -12516,10 +12546,10 @@
         </is>
       </c>
       <c r="D119" s="59" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="E119" s="46" t="n">
-        <v>0.73</v>
+        <v>0.7289</v>
       </c>
       <c r="F119" s="46" t="inlineStr">
         <is>
@@ -12528,17 +12558,17 @@
       </c>
       <c r="G119" s="46" t="n"/>
       <c r="H119" s="46" t="n">
-        <v>0.767</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I119" s="46" t="n">
-        <v>0.8525</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J119" s="46" t="n">
-        <v>0.6387</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="K119" s="46" t="n"/>
       <c r="L119" s="46" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="M119" s="46" t="n">
         <v>0.65</v>
@@ -12546,28 +12576,30 @@
       <c r="N119" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O119" s="46" t="n"/>
+      <c r="O119" s="46" t="n">
+        <v>0.436</v>
+      </c>
       <c r="P119" s="46" t="n"/>
       <c r="Q119" s="49" t="n">
-        <v>0.748</v>
+        <v>0.7925</v>
       </c>
       <c r="R119" s="49" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="S119" s="50" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="T119" s="49" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="U119" s="49" t="n">
-        <v>0.5865</v>
+        <v>0.7319</v>
       </c>
       <c r="V119" s="49" t="n">
-        <v>0.7695</v>
+        <v>0.6385</v>
       </c>
       <c r="W119" s="49" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="X119" s="49" t="inlineStr">
         <is>
@@ -12579,10 +12611,10 @@
         <v>0</v>
       </c>
       <c r="AA119" s="46" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="AB119" s="46" t="n">
-        <v>0.136</v>
+        <v>0.889</v>
+      </c>
+      <c r="AB119" s="51" t="n">
+        <v>0.698</v>
       </c>
       <c r="AC119" s="46" t="inlineStr">
         <is>
@@ -12590,13 +12622,13 @@
         </is>
       </c>
       <c r="AD119" s="46" t="n">
-        <v>0.26</v>
+        <v>0.181</v>
       </c>
       <c r="AE119" s="46" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="AF119" s="46" t="n">
-        <v>0.769</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -12901,7 +12933,7 @@
       </c>
       <c r="B123" s="47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C123" s="59" t="inlineStr">
@@ -12910,10 +12942,10 @@
         </is>
       </c>
       <c r="D123" s="59" t="n">
-        <v>0.753</v>
+        <v>0.762</v>
       </c>
       <c r="E123" s="46" t="n">
-        <v>0.7528</v>
+        <v>0.7625</v>
       </c>
       <c r="F123" s="46" t="inlineStr">
         <is>
@@ -12922,17 +12954,17 @@
       </c>
       <c r="G123" s="46" t="n"/>
       <c r="H123" s="46" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="I123" s="46" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.8525</v>
       </c>
       <c r="J123" s="46" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.6387</v>
       </c>
       <c r="K123" s="46" t="n"/>
       <c r="L123" s="46" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="M123" s="46" t="n">
         <v>0.65</v>
@@ -12940,28 +12972,30 @@
       <c r="N123" s="46" t="n">
         <v>0.7</v>
       </c>
-      <c r="O123" s="46" t="n"/>
+      <c r="O123" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="P123" s="46" t="n"/>
       <c r="Q123" s="49" t="n">
-        <v>0.7925</v>
+        <v>0.748</v>
       </c>
       <c r="R123" s="49" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="S123" s="50" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="T123" s="49" t="n">
-        <v>0.917</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="U123" s="49" t="n">
-        <v>0.7319</v>
+        <v>0.5865</v>
       </c>
       <c r="V123" s="49" t="n">
-        <v>0.6385</v>
+        <v>0.7695</v>
       </c>
       <c r="W123" s="49" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="X123" s="49" t="inlineStr">
         <is>
@@ -12973,10 +13007,10 @@
         <v>0</v>
       </c>
       <c r="AA123" s="46" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="AB123" s="51" t="n">
-        <v>0.698</v>
+        <v>0.907</v>
+      </c>
+      <c r="AB123" s="46" t="n">
+        <v>0.136</v>
       </c>
       <c r="AC123" s="46" t="inlineStr">
         <is>
@@ -12984,13 +13018,13 @@
         </is>
       </c>
       <c r="AD123" s="46" t="n">
-        <v>0.181</v>
+        <v>0.26</v>
       </c>
       <c r="AE123" s="46" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AF123" s="46" t="n">
-        <v>0.638</v>
+        <v>0.769</v>
       </c>
     </row>
     <row r="124">
@@ -13008,10 +13042,10 @@
         </is>
       </c>
       <c r="D124" s="63" t="n">
-        <v>0.766</v>
+        <v>0.791</v>
       </c>
       <c r="E124" s="55" t="n">
-        <v>0.7661</v>
+        <v>0.7906</v>
       </c>
       <c r="F124" s="55" t="inlineStr">
         <is>
@@ -13030,7 +13064,7 @@
       </c>
       <c r="K124" s="55" t="n"/>
       <c r="L124" s="55" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="M124" s="55" t="n">
         <v>0.8091</v>
@@ -13038,7 +13072,9 @@
       <c r="N124" s="55" t="n">
         <v>0.7</v>
       </c>
-      <c r="O124" s="55" t="n"/>
+      <c r="O124" s="55" t="n">
+        <v>1</v>
+      </c>
       <c r="P124" s="55" t="n"/>
       <c r="Q124" s="50" t="n">
         <v>0.8016</v>
@@ -16138,7 +16174,7 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C78" s="66" t="inlineStr">
@@ -16147,10 +16183,10 @@
         </is>
       </c>
       <c r="D78" s="66" t="n">
-        <v>0.583</v>
+        <v>0.582</v>
       </c>
       <c r="E78" s="19" t="n">
-        <v>0.6478</v>
+        <v>0.6472</v>
       </c>
       <c r="F78" s="19" t="n">
         <v>0.9</v>
@@ -16162,13 +16198,13 @@
       </c>
       <c r="H78" s="19" t="n"/>
       <c r="I78" s="19" t="n">
-        <v>0.6651</v>
+        <v>0.6888</v>
       </c>
       <c r="J78" s="19" t="n">
-        <v>0.4397</v>
+        <v>0.5275</v>
       </c>
       <c r="K78" s="19" t="n">
-        <v>0.8385</v>
+        <v>0.7254</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -16177,7 +16213,7 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C79" s="66" t="inlineStr">
@@ -16186,10 +16222,10 @@
         </is>
       </c>
       <c r="D79" s="66" t="n">
-        <v>0.584</v>
+        <v>0.583</v>
       </c>
       <c r="E79" s="19" t="n">
-        <v>0.6491</v>
+        <v>0.6478</v>
       </c>
       <c r="F79" s="19" t="n">
         <v>0.9</v>
@@ -16201,13 +16237,13 @@
       </c>
       <c r="H79" s="19" t="n"/>
       <c r="I79" s="19" t="n">
-        <v>0.6909</v>
+        <v>0.6651</v>
       </c>
       <c r="J79" s="19" t="n">
-        <v>0.4706</v>
+        <v>0.4397</v>
       </c>
       <c r="K79" s="19" t="n">
-        <v>0.7857</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -16216,19 +16252,19 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
-        </is>
-      </c>
-      <c r="C80" s="67" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="D80" s="67" t="n">
-        <v>0.589</v>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C80" s="66" t="inlineStr">
+        <is>
+          <t>Stressed</t>
+        </is>
+      </c>
+      <c r="D80" s="66" t="n">
+        <v>0.584</v>
       </c>
       <c r="E80" s="19" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.6491</v>
       </c>
       <c r="F80" s="19" t="n">
         <v>0.9</v>
@@ -16240,13 +16276,13 @@
       </c>
       <c r="H80" s="19" t="n"/>
       <c r="I80" s="19" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.6909</v>
       </c>
       <c r="J80" s="19" t="n">
-        <v>0.5394</v>
+        <v>0.4706</v>
       </c>
       <c r="K80" s="19" t="n">
-        <v>0.7216</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
@@ -16255,7 +16291,7 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="C81" s="67" t="inlineStr">
@@ -16264,10 +16300,10 @@
         </is>
       </c>
       <c r="D81" s="67" t="n">
-        <v>0.591</v>
+        <v>0.589</v>
       </c>
       <c r="E81" s="19" t="n">
-        <v>0.6571</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="F81" s="19" t="n">
         <v>0.9</v>
@@ -16279,13 +16315,13 @@
       </c>
       <c r="H81" s="19" t="n"/>
       <c r="I81" s="19" t="n">
-        <v>0.6712</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="J81" s="19" t="n">
-        <v>0.675</v>
+        <v>0.5394</v>
       </c>
       <c r="K81" s="19" t="n">
-        <v>0.625</v>
+        <v>0.7216</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
@@ -16294,7 +16330,7 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C82" s="67" t="inlineStr">
@@ -16303,10 +16339,10 @@
         </is>
       </c>
       <c r="D82" s="67" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="E82" s="19" t="n">
-        <v>0.6582</v>
+        <v>0.6571</v>
       </c>
       <c r="F82" s="19" t="n">
         <v>0.9</v>
@@ -16318,13 +16354,13 @@
       </c>
       <c r="H82" s="19" t="n"/>
       <c r="I82" s="19" t="n">
-        <v>0.616</v>
+        <v>0.6712</v>
       </c>
       <c r="J82" s="19" t="n">
-        <v>0.631</v>
+        <v>0.675</v>
       </c>
       <c r="K82" s="19" t="n">
-        <v>0.7275</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
@@ -16333,7 +16369,7 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C83" s="67" t="inlineStr">
@@ -16342,10 +16378,10 @@
         </is>
       </c>
       <c r="D83" s="67" t="n">
-        <v>0.601</v>
+        <v>0.592</v>
       </c>
       <c r="E83" s="19" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6582</v>
       </c>
       <c r="F83" s="19" t="n">
         <v>0.9</v>
@@ -16357,13 +16393,13 @@
       </c>
       <c r="H83" s="19" t="n"/>
       <c r="I83" s="19" t="n">
-        <v>0.7084</v>
+        <v>0.616</v>
       </c>
       <c r="J83" s="19" t="n">
-        <v>0.4877</v>
+        <v>0.631</v>
       </c>
       <c r="K83" s="19" t="n">
-        <v>0.8073</v>
+        <v>0.7275</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
@@ -16372,7 +16408,7 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C84" s="67" t="inlineStr">
@@ -16381,10 +16417,10 @@
         </is>
       </c>
       <c r="D84" s="67" t="n">
-        <v>0.604</v>
+        <v>0.598</v>
       </c>
       <c r="E84" s="19" t="n">
-        <v>0.6716</v>
+        <v>0.6641</v>
       </c>
       <c r="F84" s="19" t="n">
         <v>0.9</v>
@@ -16396,13 +16432,13 @@
       </c>
       <c r="H84" s="19" t="n"/>
       <c r="I84" s="19" t="n">
-        <v>0.6639</v>
+        <v>0.6923</v>
       </c>
       <c r="J84" s="19" t="n">
-        <v>0.7183</v>
+        <v>0.6213</v>
       </c>
       <c r="K84" s="19" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.6787</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -16411,7 +16447,7 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C85" s="67" t="inlineStr">
@@ -16420,28 +16456,28 @@
         </is>
       </c>
       <c r="D85" s="67" t="n">
-        <v>0.608</v>
+        <v>0.598</v>
       </c>
       <c r="E85" s="19" t="n">
-        <v>0.6752</v>
+        <v>0.5976</v>
       </c>
       <c r="F85" s="19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&gt; 180 days (post-harvest)</t>
         </is>
       </c>
       <c r="H85" s="19" t="n"/>
       <c r="I85" s="19" t="n">
-        <v>0.7052</v>
+        <v>0.7022</v>
       </c>
       <c r="J85" s="19" t="n">
-        <v>0.675</v>
+        <v>0.554</v>
       </c>
       <c r="K85" s="19" t="n">
-        <v>0.6455</v>
+        <v>0.5365</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
@@ -16450,7 +16486,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C86" s="67" t="inlineStr">
@@ -16459,10 +16495,10 @@
         </is>
       </c>
       <c r="D86" s="67" t="n">
-        <v>0.614</v>
+        <v>0.601</v>
       </c>
       <c r="E86" s="19" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="F86" s="19" t="n">
         <v>0.9</v>
@@ -16474,13 +16510,13 @@
       </c>
       <c r="H86" s="19" t="n"/>
       <c r="I86" s="19" t="n">
-        <v>0.6923</v>
+        <v>0.7084</v>
       </c>
       <c r="J86" s="19" t="n">
-        <v>0.675</v>
+        <v>0.4877</v>
       </c>
       <c r="K86" s="19" t="n">
-        <v>0.6787</v>
+        <v>0.8073</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
@@ -16489,7 +16525,7 @@
       </c>
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C87" s="67" t="inlineStr">
@@ -16498,28 +16534,28 @@
         </is>
       </c>
       <c r="D87" s="67" t="n">
-        <v>0.617</v>
+        <v>0.604</v>
       </c>
       <c r="E87" s="19" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6716</v>
       </c>
       <c r="F87" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G87" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H87" s="19" t="n"/>
       <c r="I87" s="19" t="n">
-        <v>0.6926</v>
+        <v>0.6639</v>
       </c>
       <c r="J87" s="19" t="n">
-        <v>0.6073</v>
+        <v>0.7183</v>
       </c>
       <c r="K87" s="19" t="n">
-        <v>0.6492</v>
+        <v>0.6326000000000001</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
@@ -16528,7 +16564,7 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C88" s="67" t="inlineStr">
@@ -16540,34 +16576,34 @@
         <v>0.617</v>
       </c>
       <c r="E88" s="19" t="n">
-        <v>0.6851</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="F88" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G88" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H88" s="19" t="n"/>
       <c r="I88" s="19" t="n">
-        <v>0.666</v>
+        <v>0.6926</v>
       </c>
       <c r="J88" s="19" t="n">
-        <v>0.6015</v>
+        <v>0.6073</v>
       </c>
       <c r="K88" s="19" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.6492</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C89" s="67" t="inlineStr">
@@ -16576,37 +16612,37 @@
         </is>
       </c>
       <c r="D89" s="67" t="n">
-        <v>0.621</v>
+        <v>0.617</v>
       </c>
       <c r="E89" s="19" t="n">
-        <v>0.6535</v>
+        <v>0.6851</v>
       </c>
       <c r="F89" s="19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G89" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H89" s="19" t="n"/>
       <c r="I89" s="19" t="n">
-        <v>0.7175</v>
+        <v>0.666</v>
       </c>
       <c r="J89" s="19" t="n">
-        <v>0.3839</v>
+        <v>0.6015</v>
       </c>
       <c r="K89" s="19" t="n">
-        <v>0.8591</v>
+        <v>0.7877999999999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="19" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C90" s="67" t="inlineStr">
@@ -16618,34 +16654,34 @@
         <v>0.621</v>
       </c>
       <c r="E90" s="19" t="n">
-        <v>0.6902</v>
+        <v>0.6535</v>
       </c>
       <c r="F90" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H90" s="19" t="n"/>
       <c r="I90" s="19" t="n">
-        <v>0.7611</v>
+        <v>0.7175</v>
       </c>
       <c r="J90" s="19" t="n">
-        <v>0.6288</v>
+        <v>0.3839</v>
       </c>
       <c r="K90" s="19" t="n">
-        <v>0.6808</v>
+        <v>0.8591</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="19" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C91" s="67" t="inlineStr">
@@ -16654,10 +16690,10 @@
         </is>
       </c>
       <c r="D91" s="67" t="n">
-        <v>0.622</v>
+        <v>0.621</v>
       </c>
       <c r="E91" s="19" t="n">
-        <v>0.6913</v>
+        <v>0.6902</v>
       </c>
       <c r="F91" s="19" t="n">
         <v>0.9</v>
@@ -16669,13 +16705,13 @@
       </c>
       <c r="H91" s="19" t="n"/>
       <c r="I91" s="19" t="n">
-        <v>0.6192</v>
+        <v>0.7611</v>
       </c>
       <c r="J91" s="19" t="n">
-        <v>0.7719</v>
+        <v>0.6288</v>
       </c>
       <c r="K91" s="19" t="n">
-        <v>0.6829</v>
+        <v>0.6808</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
@@ -16684,7 +16720,7 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C92" s="67" t="inlineStr">
@@ -16693,10 +16729,10 @@
         </is>
       </c>
       <c r="D92" s="67" t="n">
-        <v>0.625</v>
+        <v>0.622</v>
       </c>
       <c r="E92" s="19" t="n">
-        <v>0.6939</v>
+        <v>0.6913</v>
       </c>
       <c r="F92" s="19" t="n">
         <v>0.9</v>
@@ -16708,13 +16744,13 @@
       </c>
       <c r="H92" s="19" t="n"/>
       <c r="I92" s="19" t="n">
-        <v>0.774</v>
+        <v>0.6192</v>
       </c>
       <c r="J92" s="19" t="n">
-        <v>0.4124</v>
+        <v>0.7719</v>
       </c>
       <c r="K92" s="19" t="n">
-        <v>0.8952</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
@@ -16723,7 +16759,7 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C93" s="67" t="inlineStr">
@@ -16732,10 +16768,10 @@
         </is>
       </c>
       <c r="D93" s="67" t="n">
-        <v>0.627</v>
+        <v>0.625</v>
       </c>
       <c r="E93" s="19" t="n">
-        <v>0.6964</v>
+        <v>0.6939</v>
       </c>
       <c r="F93" s="19" t="n">
         <v>0.9</v>
@@ -16747,13 +16783,13 @@
       </c>
       <c r="H93" s="19" t="n"/>
       <c r="I93" s="19" t="n">
-        <v>0.6888</v>
+        <v>0.774</v>
       </c>
       <c r="J93" s="19" t="n">
-        <v>0.675</v>
+        <v>0.4124</v>
       </c>
       <c r="K93" s="19" t="n">
-        <v>0.7254</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
@@ -16840,7 +16876,7 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C96" s="67" t="inlineStr">
@@ -16849,10 +16885,10 @@
         </is>
       </c>
       <c r="D96" s="67" t="n">
-        <v>0.635</v>
+        <v>0.637</v>
       </c>
       <c r="E96" s="19" t="n">
-        <v>0.7052</v>
+        <v>0.7077</v>
       </c>
       <c r="F96" s="19" t="n">
         <v>0.9</v>
@@ -16864,13 +16900,13 @@
       </c>
       <c r="H96" s="19" t="n"/>
       <c r="I96" s="19" t="n">
-        <v>0.7153</v>
+        <v>0.7052</v>
       </c>
       <c r="J96" s="19" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="K96" s="19" t="n">
-        <v>0.7252</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
@@ -16879,7 +16915,7 @@
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C97" s="67" t="inlineStr">
@@ -16888,28 +16924,28 @@
         </is>
       </c>
       <c r="D97" s="67" t="n">
-        <v>0.638</v>
+        <v>0.64</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>0.6379</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
-          <t>&gt; 180 days (post-harvest)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H97" s="19" t="n"/>
       <c r="I97" s="19" t="n">
-        <v>0.7022</v>
+        <v>0.7534</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>0.675</v>
+        <v>0.5002</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>0.5365</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
@@ -16918,37 +16954,37 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C98" s="67" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="D98" s="67" t="n">
-        <v>0.64</v>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C98" s="68" t="inlineStr">
+        <is>
+          <t>Insulated</t>
+        </is>
+      </c>
+      <c r="D98" s="68" t="n">
+        <v>0.649</v>
       </c>
       <c r="E98" s="19" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6495</v>
       </c>
       <c r="F98" s="19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G98" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&gt; 180 days (post-harvest)</t>
         </is>
       </c>
       <c r="H98" s="19" t="n"/>
       <c r="I98" s="19" t="n">
-        <v>0.7534</v>
+        <v>0.6812</v>
       </c>
       <c r="J98" s="19" t="n">
-        <v>0.5002</v>
+        <v>0.675</v>
       </c>
       <c r="K98" s="19" t="n">
-        <v>0.88</v>
+        <v>0.5921999999999999</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
@@ -16957,7 +16993,7 @@
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C99" s="68" t="inlineStr">
@@ -16966,10 +17002,10 @@
         </is>
       </c>
       <c r="D99" s="68" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="E99" s="19" t="n">
-        <v>0.7156</v>
+        <v>0.7206</v>
       </c>
       <c r="F99" s="19" t="n">
         <v>0.9</v>
@@ -16981,13 +17017,13 @@
       </c>
       <c r="H99" s="19" t="n"/>
       <c r="I99" s="19" t="n">
-        <v>0.7298</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J99" s="19" t="n">
-        <v>0.675</v>
+        <v>0.6984</v>
       </c>
       <c r="K99" s="19" t="n">
-        <v>0.742</v>
+        <v>0.7521</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -16996,7 +17032,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C100" s="68" t="inlineStr">
@@ -17005,28 +17041,28 @@
         </is>
       </c>
       <c r="D100" s="68" t="n">
-        <v>0.646</v>
+        <v>0.655</v>
       </c>
       <c r="E100" s="19" t="n">
-        <v>0.7179</v>
+        <v>0.655</v>
       </c>
       <c r="F100" s="19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&gt; 180 days (post-harvest)</t>
         </is>
       </c>
       <c r="H100" s="19" t="n"/>
       <c r="I100" s="19" t="n">
-        <v>0.7784</v>
+        <v>0.7463</v>
       </c>
       <c r="J100" s="19" t="n">
-        <v>0.675</v>
+        <v>0.4928</v>
       </c>
       <c r="K100" s="19" t="n">
-        <v>0.7002</v>
+        <v>0.7259</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
@@ -17035,7 +17071,7 @@
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C101" s="68" t="inlineStr">
@@ -17044,28 +17080,28 @@
         </is>
       </c>
       <c r="D101" s="68" t="n">
-        <v>0.649</v>
+        <v>0.664</v>
       </c>
       <c r="E101" s="19" t="n">
-        <v>0.6495</v>
+        <v>0.7377</v>
       </c>
       <c r="F101" s="19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G101" s="23" t="inlineStr">
         <is>
-          <t>&gt; 180 days (post-harvest)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H101" s="19" t="n"/>
       <c r="I101" s="19" t="n">
-        <v>0.6812</v>
+        <v>0.7153</v>
       </c>
       <c r="J101" s="19" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="K101" s="19" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.7252</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
@@ -17074,7 +17110,7 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C102" s="68" t="inlineStr">
@@ -17083,28 +17119,28 @@
         </is>
       </c>
       <c r="D102" s="68" t="n">
-        <v>0.649</v>
+        <v>0.667</v>
       </c>
       <c r="E102" s="19" t="n">
-        <v>0.7206</v>
+        <v>0.6671</v>
       </c>
       <c r="F102" s="19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>&gt; 180 days (post-harvest)</t>
         </is>
       </c>
       <c r="H102" s="19" t="n"/>
       <c r="I102" s="19" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.709</v>
       </c>
       <c r="J102" s="19" t="n">
-        <v>0.6984</v>
+        <v>0.675</v>
       </c>
       <c r="K102" s="19" t="n">
-        <v>0.7521</v>
+        <v>0.6173</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
@@ -17113,7 +17149,7 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C103" s="68" t="inlineStr">
@@ -17122,10 +17158,10 @@
         </is>
       </c>
       <c r="D103" s="68" t="n">
-        <v>0.661</v>
+        <v>0.673</v>
       </c>
       <c r="E103" s="19" t="n">
-        <v>0.7347</v>
+        <v>0.7481</v>
       </c>
       <c r="F103" s="19" t="n">
         <v>0.9</v>
@@ -17137,13 +17173,13 @@
       </c>
       <c r="H103" s="19" t="n"/>
       <c r="I103" s="19" t="n">
-        <v>0.7733</v>
+        <v>0.7298</v>
       </c>
       <c r="J103" s="19" t="n">
-        <v>0.7</v>
+        <v>0.7725</v>
       </c>
       <c r="K103" s="19" t="n">
-        <v>0.7309</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
@@ -17152,7 +17188,7 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C104" s="68" t="inlineStr">
@@ -17161,10 +17197,10 @@
         </is>
       </c>
       <c r="D104" s="68" t="n">
-        <v>0.662</v>
+        <v>0.675</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>0.736</v>
+        <v>0.7504</v>
       </c>
       <c r="F104" s="19" t="n">
         <v>0.9</v>
@@ -17176,13 +17212,13 @@
       </c>
       <c r="H104" s="19" t="n"/>
       <c r="I104" s="19" t="n">
-        <v>0.7859</v>
+        <v>0.7784</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>0.7471</v>
+        <v>0.7002</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -17191,7 +17227,7 @@
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C105" s="68" t="inlineStr">
@@ -17200,37 +17236,31 @@
         </is>
       </c>
       <c r="D105" s="68" t="n">
-        <v>0.667</v>
+        <v>0.675</v>
       </c>
       <c r="E105" s="19" t="n">
-        <v>0.6671</v>
-      </c>
-      <c r="F105" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="23" t="inlineStr">
-        <is>
-          <t>&gt; 180 days (post-harvest)</t>
-        </is>
-      </c>
+        <v>0.7504</v>
+      </c>
+      <c r="F105" s="19" t="n"/>
+      <c r="G105" s="23" t="n"/>
       <c r="H105" s="19" t="n"/>
       <c r="I105" s="19" t="n">
-        <v>0.709</v>
+        <v>0.8007</v>
       </c>
       <c r="J105" s="19" t="n">
-        <v>0.675</v>
+        <v>0.5769</v>
       </c>
       <c r="K105" s="19" t="n">
-        <v>0.6173</v>
+        <v>0.8735000000000001</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="19" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C106" s="68" t="inlineStr">
@@ -17239,37 +17269,37 @@
         </is>
       </c>
       <c r="D106" s="68" t="n">
-        <v>0.671</v>
+        <v>0.678</v>
       </c>
       <c r="E106" s="19" t="n">
-        <v>0.7458</v>
+        <v>0.714</v>
       </c>
       <c r="F106" s="19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G106" s="23" t="inlineStr">
         <is>
-          <t>30–90 days</t>
+          <t>90–180 days</t>
         </is>
       </c>
       <c r="H106" s="19" t="n"/>
       <c r="I106" s="19" t="n">
-        <v>0.7701</v>
+        <v>0.6857</v>
       </c>
       <c r="J106" s="19" t="n">
-        <v>0.675</v>
+        <v>0.6515</v>
       </c>
       <c r="K106" s="19" t="n">
-        <v>0.7924</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="19" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C107" s="68" t="inlineStr">
@@ -17278,31 +17308,37 @@
         </is>
       </c>
       <c r="D107" s="68" t="n">
-        <v>0.675</v>
+        <v>0.678</v>
       </c>
       <c r="E107" s="19" t="n">
-        <v>0.7504</v>
-      </c>
-      <c r="F107" s="19" t="n"/>
-      <c r="G107" s="23" t="n"/>
+        <v>0.6783</v>
+      </c>
+      <c r="F107" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t>&gt; 180 days (post-harvest)</t>
+        </is>
+      </c>
       <c r="H107" s="19" t="n"/>
       <c r="I107" s="19" t="n">
-        <v>0.8007</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J107" s="19" t="n">
-        <v>0.5769</v>
+        <v>0.5282</v>
       </c>
       <c r="K107" s="19" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.7722</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C108" s="68" t="inlineStr">
@@ -17314,34 +17350,34 @@
         <v>0.678</v>
       </c>
       <c r="E108" s="19" t="n">
-        <v>0.714</v>
+        <v>0.6785</v>
       </c>
       <c r="F108" s="19" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G108" s="23" t="inlineStr">
         <is>
-          <t>90–180 days</t>
+          <t>&gt; 180 days (post-harvest)</t>
         </is>
       </c>
       <c r="H108" s="19" t="n"/>
       <c r="I108" s="19" t="n">
-        <v>0.6857</v>
+        <v>0.7318</v>
       </c>
       <c r="J108" s="19" t="n">
-        <v>0.6515</v>
+        <v>0.6223</v>
       </c>
       <c r="K108" s="19" t="n">
-        <v>0.8048</v>
+        <v>0.6815</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C109" s="68" t="inlineStr">
@@ -17350,28 +17386,28 @@
         </is>
       </c>
       <c r="D109" s="68" t="n">
-        <v>0.678</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E109" s="19" t="n">
-        <v>0.6783</v>
+        <v>0.7589</v>
       </c>
       <c r="F109" s="19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G109" s="23" t="inlineStr">
         <is>
-          <t>&gt; 180 days (post-harvest)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H109" s="19" t="n"/>
       <c r="I109" s="19" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="J109" s="19" t="n">
-        <v>0.5282</v>
+        <v>0.7725</v>
       </c>
       <c r="K109" s="19" t="n">
-        <v>0.7722</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -17380,7 +17416,7 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C110" s="68" t="inlineStr">
@@ -17389,10 +17425,10 @@
         </is>
       </c>
       <c r="D110" s="68" t="n">
-        <v>0.678</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E110" s="19" t="n">
-        <v>0.6785</v>
+        <v>0.6891</v>
       </c>
       <c r="F110" s="19" t="n">
         <v>1</v>
@@ -17404,13 +17440,13 @@
       </c>
       <c r="H110" s="19" t="n"/>
       <c r="I110" s="19" t="n">
-        <v>0.7318</v>
+        <v>0.755</v>
       </c>
       <c r="J110" s="19" t="n">
-        <v>0.6223</v>
+        <v>0.675</v>
       </c>
       <c r="K110" s="19" t="n">
-        <v>0.6815</v>
+        <v>0.6372</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
@@ -17419,7 +17455,7 @@
       </c>
       <c r="B111" s="20" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C111" s="68" t="inlineStr">
@@ -17428,10 +17464,10 @@
         </is>
       </c>
       <c r="D111" s="68" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E111" s="19" t="n">
-        <v>0.7617</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F111" s="19" t="n">
         <v>0.9</v>
@@ -17443,13 +17479,13 @@
       </c>
       <c r="H111" s="19" t="n"/>
       <c r="I111" s="19" t="n">
-        <v>0.7104</v>
+        <v>0.7338</v>
       </c>
       <c r="J111" s="19" t="n">
-        <v>0.774</v>
+        <v>0.85</v>
       </c>
       <c r="K111" s="19" t="n">
-        <v>0.8007</v>
+        <v>0.7159</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
@@ -17458,7 +17494,7 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C112" s="68" t="inlineStr">
@@ -17467,28 +17503,28 @@
         </is>
       </c>
       <c r="D112" s="68" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E112" s="19" t="n">
-        <v>0.6891</v>
+        <v>0.7685</v>
       </c>
       <c r="F112" s="19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G112" s="23" t="inlineStr">
         <is>
-          <t>&gt; 180 days (post-harvest)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H112" s="19" t="n"/>
       <c r="I112" s="19" t="n">
-        <v>0.755</v>
+        <v>0.7859</v>
       </c>
       <c r="J112" s="19" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="K112" s="19" t="n">
-        <v>0.6372</v>
+        <v>0.7471</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
@@ -17497,7 +17533,7 @@
       </c>
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C113" s="68" t="inlineStr">
@@ -17506,10 +17542,10 @@
         </is>
       </c>
       <c r="D113" s="68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E113" s="19" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7783</v>
       </c>
       <c r="F113" s="19" t="n">
         <v>0.9</v>
@@ -17521,13 +17557,13 @@
       </c>
       <c r="H113" s="19" t="n"/>
       <c r="I113" s="19" t="n">
-        <v>0.7338</v>
+        <v>0.7701</v>
       </c>
       <c r="J113" s="19" t="n">
-        <v>0.85</v>
+        <v>0.7725</v>
       </c>
       <c r="K113" s="19" t="n">
-        <v>0.7159</v>
+        <v>0.7924</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
@@ -17536,7 +17572,7 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C114" s="68" t="inlineStr">
@@ -17545,10 +17581,10 @@
         </is>
       </c>
       <c r="D114" s="68" t="n">
-        <v>0.704</v>
+        <v>0.706</v>
       </c>
       <c r="E114" s="19" t="n">
-        <v>0.7825</v>
+        <v>0.7843</v>
       </c>
       <c r="F114" s="19" t="n">
         <v>0.9</v>
@@ -17560,13 +17596,13 @@
       </c>
       <c r="H114" s="19" t="n"/>
       <c r="I114" s="19" t="n">
-        <v>0.756</v>
+        <v>0.7104</v>
       </c>
       <c r="J114" s="19" t="n">
-        <v>0.85</v>
+        <v>0.8418</v>
       </c>
       <c r="K114" s="19" t="n">
-        <v>0.7415</v>
+        <v>0.8007</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -17653,7 +17689,7 @@
       </c>
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C117" s="68" t="inlineStr">
@@ -17662,28 +17698,28 @@
         </is>
       </c>
       <c r="D117" s="68" t="n">
-        <v>0.716</v>
+        <v>0.718</v>
       </c>
       <c r="E117" s="19" t="n">
-        <v>0.7157</v>
+        <v>0.7975</v>
       </c>
       <c r="F117" s="19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G117" s="23" t="inlineStr">
         <is>
-          <t>&gt; 180 days (post-harvest)</t>
+          <t>30–90 days</t>
         </is>
       </c>
       <c r="H117" s="19" t="n"/>
       <c r="I117" s="19" t="n">
-        <v>0.7463</v>
+        <v>0.756</v>
       </c>
       <c r="J117" s="19" t="n">
-        <v>0.675</v>
+        <v>0.895</v>
       </c>
       <c r="K117" s="19" t="n">
-        <v>0.7259</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
@@ -17731,7 +17767,7 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C119" s="68" t="inlineStr">
@@ -17740,10 +17776,10 @@
         </is>
       </c>
       <c r="D119" s="68" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="E119" s="19" t="n">
-        <v>0.73</v>
+        <v>0.7289</v>
       </c>
       <c r="F119" s="19" t="n">
         <v>1</v>
@@ -17755,13 +17791,13 @@
       </c>
       <c r="H119" s="19" t="n"/>
       <c r="I119" s="19" t="n">
-        <v>0.767</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J119" s="19" t="n">
-        <v>0.675</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K119" s="19" t="n">
-        <v>0.748</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -17887,7 +17923,7 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C123" s="68" t="inlineStr">
@@ -17896,10 +17932,10 @@
         </is>
       </c>
       <c r="D123" s="68" t="n">
-        <v>0.753</v>
+        <v>0.762</v>
       </c>
       <c r="E123" s="19" t="n">
-        <v>0.7528</v>
+        <v>0.7625</v>
       </c>
       <c r="F123" s="19" t="n">
         <v>1</v>
@@ -17911,13 +17947,13 @@
       </c>
       <c r="H123" s="19" t="n"/>
       <c r="I123" s="19" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="J123" s="19" t="n">
-        <v>0.675</v>
+        <v>0.7725</v>
       </c>
       <c r="K123" s="19" t="n">
-        <v>0.7925</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="124">
@@ -17935,10 +17971,10 @@
         </is>
       </c>
       <c r="D124" s="63" t="n">
-        <v>0.766</v>
+        <v>0.791</v>
       </c>
       <c r="E124" t="n">
-        <v>0.7661</v>
+        <v>0.7906</v>
       </c>
       <c r="F124" t="n">
         <v>1</v>
@@ -17952,7 +17988,7 @@
         <v>0.742</v>
       </c>
       <c r="J124" t="n">
-        <v>0.7546</v>
+        <v>0.8282</v>
       </c>
       <c r="K124" t="n">
         <v>0.8016</v>
